--- a/FRE_v015.xlsx
+++ b/FRE_v015.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\felip\Desktop\DOCUMENTOS APROVAÇÃO EMPREEDIMENTOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90D15F64-A751-4101-8844-E4CA8DD0B767}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74D1E229-C597-4ED8-B087-67F8539BBE13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="752" activeTab="1" xr2:uid="{6D66FF99-DDE4-43BB-AE9F-A56BFD2D93BD}"/>
   </bookViews>
@@ -325,7 +325,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1795" uniqueCount="901">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1796" uniqueCount="902">
   <si>
     <t>Apoio à Produção de Imóveis - Pessoa Jurídica</t>
   </si>
@@ -3098,6 +3098,9 @@
   </si>
   <si>
     <t>{DOC. PROPONENTE}</t>
+  </si>
+  <si>
+    <t>{VALOR DO TERRENO}</t>
   </si>
 </sst>
 </file>
@@ -4496,72 +4499,40 @@
     </xf>
     <xf numFmtId="10" fontId="38" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="8" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="17" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="36" fillId="0" borderId="18" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="36" fillId="0" borderId="19" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="170" fontId="19" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="170" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="14" fontId="19" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="14" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="8" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="8" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="8" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="8" fontId="19" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="8" fontId="19" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4569,52 +4540,110 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="8" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="41" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="9" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="9" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="9" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="5" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -4670,142 +4699,129 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="8" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="8" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="19" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="19" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="8" fontId="41" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="8" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="19" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="19" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="19" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="8" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="8" fontId="19" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="19" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="17" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="36" fillId="0" borderId="18" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="36" fillId="0" borderId="19" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="170" fontId="19" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="170" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="19" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="19" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4822,19 +4838,6 @@
     <xf numFmtId="10" fontId="19" fillId="0" borderId="11" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
@@ -4847,9 +4850,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4872,6 +4872,9 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="11">
@@ -5030,6 +5033,12 @@
     </dxf>
     <dxf>
       <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <color indexed="9"/>
       </font>
       <fill>
@@ -5037,12 +5046,6 @@
           <bgColor indexed="9"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -5172,13 +5175,8 @@
         <i val="0"/>
         <condense val="0"/>
         <extend val="0"/>
-        <color indexed="9"/>
+        <color auto="1"/>
       </font>
-      <fill>
-        <patternFill>
-          <bgColor indexed="9"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -5209,8 +5207,13 @@
         <i val="0"/>
         <condense val="0"/>
         <extend val="0"/>
-        <color auto="1"/>
+        <color indexed="9"/>
       </font>
+      <fill>
+        <patternFill>
+          <bgColor indexed="9"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -5272,6 +5275,8 @@
       <font>
         <b/>
         <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
       </font>
       <fill>
         <patternFill>
@@ -5294,8 +5299,6 @@
       <font>
         <b/>
         <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
       </font>
       <fill>
         <patternFill>
@@ -5751,8 +5754,8 @@
         <color indexed="9"/>
       </font>
       <fill>
-        <patternFill>
-          <bgColor indexed="9"/>
+        <patternFill patternType="none">
+          <bgColor indexed="65"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5763,8 +5766,8 @@
         <color indexed="9"/>
       </font>
       <fill>
-        <patternFill patternType="none">
-          <bgColor indexed="65"/>
+        <patternFill>
+          <bgColor indexed="9"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5779,16 +5782,16 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <i val="0"/>
-        <color auto="1"/>
+        <b val="0"/>
+        <i/>
+        <color rgb="FFC00000"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i/>
-        <color rgb="FFC00000"/>
+        <b/>
+        <i val="0"/>
+        <color auto="1"/>
       </font>
     </dxf>
     <dxf>
@@ -6377,7 +6380,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="FRE!$B$186:$O$196" spid="_x0000_s22639"/>
+                  <a14:cameraTool cellRange="FRE!$B$186:$O$196" spid="_x0000_s22642"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -6450,7 +6453,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="FRE!$B$222:$G$227" spid="_x0000_s22640"/>
+                  <a14:cameraTool cellRange="FRE!$B$222:$G$227" spid="_x0000_s22643"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -6528,7 +6531,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="FRE!$B$6:$O$19" spid="_x0000_s22641"/>
+                  <a14:cameraTool cellRange="FRE!$B$6:$O$19" spid="_x0000_s22644"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -6686,7 +6689,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="FRE!$B$222:$G$227" spid="_x0000_s19074"/>
+                  <a14:cameraTool cellRange="FRE!$B$222:$G$227" spid="_x0000_s19076"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -6764,7 +6767,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="FRE!$B$6:$O$19" spid="_x0000_s19075"/>
+                  <a14:cameraTool cellRange="FRE!$B$6:$O$19" spid="_x0000_s19077"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -6922,7 +6925,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="FRE!$B$222:$G$227" spid="_x0000_s21809"/>
+                  <a14:cameraTool cellRange="FRE!$B$222:$G$227" spid="_x0000_s21811"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -7000,7 +7003,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="FRE!$B$6:$O$19" spid="_x0000_s21810"/>
+                  <a14:cameraTool cellRange="FRE!$B$6:$O$19" spid="_x0000_s21812"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -7158,7 +7161,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="FRE!$B$222:$G$227" spid="_x0000_s19974"/>
+                  <a14:cameraTool cellRange="FRE!$B$222:$G$227" spid="_x0000_s19976"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -7236,7 +7239,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="FRE!$B$6:$O$19" spid="_x0000_s19975"/>
+                  <a14:cameraTool cellRange="FRE!$B$6:$O$19" spid="_x0000_s19977"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -7394,7 +7397,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="Orç_sintético_Hab!$B$88:$M$93" spid="_x0000_s20999"/>
+                  <a14:cameraTool cellRange="Orç_sintético_Hab!$B$88:$M$93" spid="_x0000_s21001"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -7472,7 +7475,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="FRE!$B$6:$O$19" spid="_x0000_s21000"/>
+                  <a14:cameraTool cellRange="FRE!$B$6:$O$19" spid="_x0000_s21002"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -7933,10 +7936,10 @@
       <c r="A1" s="232" t="s">
         <v>60</v>
       </c>
-      <c r="N1" s="321" t="s">
+      <c r="N1" s="242" t="s">
         <v>857</v>
       </c>
-      <c r="O1" s="322"/>
+      <c r="O1" s="243"/>
       <c r="P1" s="10"/>
     </row>
     <row r="2" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
@@ -7946,10 +7949,10 @@
       <c r="F2" s="144" t="s">
         <v>69</v>
       </c>
-      <c r="N2" s="323" t="s">
+      <c r="N2" s="244" t="s">
         <v>858</v>
       </c>
-      <c r="O2" s="324"/>
+      <c r="O2" s="245"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" s="232" t="s">
@@ -7965,14 +7968,14 @@
       <c r="D4" s="104" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="256" t="s">
-        <v>0</v>
-      </c>
-      <c r="F4" s="256"/>
-      <c r="G4" s="256"/>
-      <c r="H4" s="256"/>
-      <c r="I4" s="256"/>
-      <c r="J4" s="256"/>
+      <c r="E4" s="315" t="s">
+        <v>0</v>
+      </c>
+      <c r="F4" s="315"/>
+      <c r="G4" s="315"/>
+      <c r="H4" s="315"/>
+      <c r="I4" s="315"/>
+      <c r="J4" s="315"/>
       <c r="K4" s="122"/>
       <c r="L4" s="122"/>
       <c r="M4" s="122"/>
@@ -8009,22 +8012,22 @@
       <c r="A7" s="232" t="s">
         <v>851</v>
       </c>
-      <c r="B7" s="292" t="s">
+      <c r="B7" s="261" t="s">
         <v>876</v>
       </c>
-      <c r="C7" s="293"/>
-      <c r="D7" s="293"/>
-      <c r="E7" s="293"/>
-      <c r="F7" s="293"/>
-      <c r="G7" s="293"/>
-      <c r="H7" s="293"/>
-      <c r="I7" s="293"/>
-      <c r="J7" s="293"/>
-      <c r="K7" s="293"/>
-      <c r="L7" s="293"/>
-      <c r="M7" s="293"/>
-      <c r="N7" s="293"/>
-      <c r="O7" s="293"/>
+      <c r="C7" s="262"/>
+      <c r="D7" s="262"/>
+      <c r="E7" s="262"/>
+      <c r="F7" s="262"/>
+      <c r="G7" s="262"/>
+      <c r="H7" s="262"/>
+      <c r="I7" s="262"/>
+      <c r="J7" s="262"/>
+      <c r="K7" s="262"/>
+      <c r="L7" s="262"/>
+      <c r="M7" s="262"/>
+      <c r="N7" s="262"/>
+      <c r="O7" s="262"/>
     </row>
     <row r="8" spans="1:16" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="232" t="s">
@@ -8069,24 +8072,24 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" s="232"/>
-      <c r="B10" s="292" t="s">
+      <c r="B10" s="261" t="s">
         <v>877</v>
       </c>
-      <c r="C10" s="293"/>
-      <c r="D10" s="293"/>
-      <c r="E10" s="293"/>
-      <c r="F10" s="293"/>
-      <c r="G10" s="293"/>
-      <c r="H10" s="293"/>
-      <c r="I10" s="293"/>
-      <c r="J10" s="293"/>
-      <c r="K10" s="293"/>
-      <c r="L10" s="294"/>
-      <c r="M10" s="295" t="s">
+      <c r="C10" s="262"/>
+      <c r="D10" s="262"/>
+      <c r="E10" s="262"/>
+      <c r="F10" s="262"/>
+      <c r="G10" s="262"/>
+      <c r="H10" s="262"/>
+      <c r="I10" s="262"/>
+      <c r="J10" s="262"/>
+      <c r="K10" s="262"/>
+      <c r="L10" s="283"/>
+      <c r="M10" s="278" t="s">
         <v>878</v>
       </c>
-      <c r="N10" s="297"/>
-      <c r="O10" s="296"/>
+      <c r="N10" s="279"/>
+      <c r="O10" s="282"/>
     </row>
     <row r="11" spans="1:16" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="231"/>
@@ -8128,28 +8131,28 @@
       <c r="O12" s="206"/>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B13" s="292" t="s">
+      <c r="B13" s="261" t="s">
         <v>879</v>
       </c>
-      <c r="C13" s="293"/>
-      <c r="D13" s="293"/>
-      <c r="E13" s="293"/>
-      <c r="F13" s="293"/>
-      <c r="G13" s="293"/>
-      <c r="H13" s="294"/>
-      <c r="I13" s="295" t="s">
+      <c r="C13" s="262"/>
+      <c r="D13" s="262"/>
+      <c r="E13" s="262"/>
+      <c r="F13" s="262"/>
+      <c r="G13" s="262"/>
+      <c r="H13" s="283"/>
+      <c r="I13" s="278" t="s">
         <v>880</v>
       </c>
-      <c r="J13" s="297"/>
-      <c r="K13" s="297"/>
-      <c r="L13" s="296"/>
+      <c r="J13" s="279"/>
+      <c r="K13" s="279"/>
+      <c r="L13" s="282"/>
       <c r="M13" s="208" t="s">
         <v>859</v>
       </c>
-      <c r="N13" s="295" t="s">
+      <c r="N13" s="278" t="s">
         <v>881</v>
       </c>
-      <c r="O13" s="296"/>
+      <c r="O13" s="282"/>
     </row>
     <row r="14" spans="1:16" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="180"/>
@@ -8186,24 +8189,24 @@
       <c r="O15" s="206"/>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B16" s="298" t="s">
+      <c r="B16" s="275" t="s">
         <v>882</v>
       </c>
-      <c r="C16" s="299"/>
-      <c r="D16" s="299"/>
-      <c r="E16" s="299"/>
-      <c r="F16" s="299"/>
-      <c r="G16" s="299"/>
-      <c r="H16" s="299"/>
-      <c r="I16" s="299"/>
-      <c r="J16" s="299"/>
-      <c r="K16" s="299"/>
-      <c r="L16" s="300"/>
-      <c r="M16" s="295" t="s">
+      <c r="C16" s="276"/>
+      <c r="D16" s="276"/>
+      <c r="E16" s="276"/>
+      <c r="F16" s="276"/>
+      <c r="G16" s="276"/>
+      <c r="H16" s="276"/>
+      <c r="I16" s="276"/>
+      <c r="J16" s="276"/>
+      <c r="K16" s="276"/>
+      <c r="L16" s="277"/>
+      <c r="M16" s="278" t="s">
         <v>900</v>
       </c>
-      <c r="N16" s="297"/>
-      <c r="O16" s="297"/>
+      <c r="N16" s="279"/>
+      <c r="O16" s="279"/>
     </row>
     <row r="17" spans="2:15" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="180"/>
@@ -8240,24 +8243,24 @@
       <c r="O18" s="206"/>
     </row>
     <row r="19" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B19" s="301" t="s">
+      <c r="B19" s="265" t="s">
         <v>883</v>
       </c>
-      <c r="C19" s="302"/>
-      <c r="D19" s="302"/>
-      <c r="E19" s="302"/>
-      <c r="F19" s="302"/>
-      <c r="G19" s="302"/>
-      <c r="H19" s="302"/>
-      <c r="I19" s="302"/>
-      <c r="J19" s="302"/>
-      <c r="K19" s="302"/>
-      <c r="L19" s="303"/>
-      <c r="M19" s="295" t="s">
+      <c r="C19" s="266"/>
+      <c r="D19" s="266"/>
+      <c r="E19" s="266"/>
+      <c r="F19" s="266"/>
+      <c r="G19" s="266"/>
+      <c r="H19" s="266"/>
+      <c r="I19" s="266"/>
+      <c r="J19" s="266"/>
+      <c r="K19" s="266"/>
+      <c r="L19" s="267"/>
+      <c r="M19" s="278" t="s">
         <v>884</v>
       </c>
-      <c r="N19" s="297"/>
-      <c r="O19" s="297"/>
+      <c r="N19" s="279"/>
+      <c r="O19" s="279"/>
     </row>
     <row r="20" spans="2:15" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="180"/>
@@ -8296,26 +8299,26 @@
       <c r="O21" s="206"/>
     </row>
     <row r="22" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B22" s="301" t="s">
+      <c r="B22" s="265" t="s">
         <v>885</v>
       </c>
-      <c r="C22" s="302"/>
-      <c r="D22" s="302"/>
-      <c r="E22" s="302"/>
-      <c r="F22" s="302"/>
-      <c r="G22" s="302"/>
-      <c r="H22" s="302"/>
-      <c r="I22" s="303"/>
-      <c r="J22" s="313" t="s">
+      <c r="C22" s="266"/>
+      <c r="D22" s="266"/>
+      <c r="E22" s="266"/>
+      <c r="F22" s="266"/>
+      <c r="G22" s="266"/>
+      <c r="H22" s="266"/>
+      <c r="I22" s="267"/>
+      <c r="J22" s="268" t="s">
         <v>887</v>
       </c>
-      <c r="K22" s="314"/>
-      <c r="L22" s="315"/>
-      <c r="M22" s="316" t="s">
+      <c r="K22" s="269"/>
+      <c r="L22" s="270"/>
+      <c r="M22" s="271" t="s">
         <v>886</v>
       </c>
-      <c r="N22" s="317"/>
-      <c r="O22" s="318"/>
+      <c r="N22" s="272"/>
+      <c r="O22" s="273"/>
     </row>
     <row r="23" spans="2:15" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="180"/>
@@ -8352,24 +8355,24 @@
       <c r="O24" s="206"/>
     </row>
     <row r="25" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B25" s="298" t="s">
+      <c r="B25" s="275" t="s">
         <v>888</v>
       </c>
-      <c r="C25" s="299"/>
-      <c r="D25" s="299"/>
-      <c r="E25" s="299"/>
-      <c r="F25" s="299"/>
-      <c r="G25" s="299"/>
-      <c r="H25" s="299"/>
-      <c r="I25" s="299"/>
-      <c r="J25" s="299"/>
-      <c r="K25" s="299"/>
-      <c r="L25" s="300"/>
-      <c r="M25" s="295" t="s">
+      <c r="C25" s="276"/>
+      <c r="D25" s="276"/>
+      <c r="E25" s="276"/>
+      <c r="F25" s="276"/>
+      <c r="G25" s="276"/>
+      <c r="H25" s="276"/>
+      <c r="I25" s="276"/>
+      <c r="J25" s="276"/>
+      <c r="K25" s="276"/>
+      <c r="L25" s="277"/>
+      <c r="M25" s="278" t="s">
         <v>889</v>
       </c>
-      <c r="N25" s="297"/>
-      <c r="O25" s="297"/>
+      <c r="N25" s="279"/>
+      <c r="O25" s="279"/>
     </row>
     <row r="26" spans="2:15" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="180"/>
@@ -8408,26 +8411,26 @@
       <c r="O27" s="206"/>
     </row>
     <row r="28" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="301" t="s">
+      <c r="B28" s="265" t="s">
         <v>885</v>
       </c>
-      <c r="C28" s="302"/>
-      <c r="D28" s="302"/>
-      <c r="E28" s="302"/>
-      <c r="F28" s="302"/>
-      <c r="G28" s="302"/>
-      <c r="H28" s="302"/>
-      <c r="I28" s="303"/>
-      <c r="J28" s="274" t="s">
+      <c r="C28" s="266"/>
+      <c r="D28" s="266"/>
+      <c r="E28" s="266"/>
+      <c r="F28" s="266"/>
+      <c r="G28" s="266"/>
+      <c r="H28" s="266"/>
+      <c r="I28" s="267"/>
+      <c r="J28" s="319" t="s">
         <v>890</v>
       </c>
-      <c r="K28" s="275"/>
-      <c r="L28" s="276"/>
-      <c r="M28" s="277" t="s">
+      <c r="K28" s="320"/>
+      <c r="L28" s="321"/>
+      <c r="M28" s="285" t="s">
         <v>891</v>
       </c>
-      <c r="N28" s="278"/>
-      <c r="O28" s="279"/>
+      <c r="N28" s="286"/>
+      <c r="O28" s="287"/>
     </row>
     <row r="29" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B29" s="145"/>
@@ -8459,8 +8462,8 @@
       <c r="I30" s="207" t="s">
         <v>841</v>
       </c>
-      <c r="J30" s="280"/>
-      <c r="K30" s="280"/>
+      <c r="J30" s="288"/>
+      <c r="K30" s="288"/>
       <c r="L30" s="212"/>
       <c r="M30" s="212"/>
       <c r="N30" s="212"/>
@@ -8491,10 +8494,10 @@
       <c r="E34" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="F34" s="259" t="s">
+      <c r="F34" s="316" t="s">
         <v>861</v>
       </c>
-      <c r="G34" s="259"/>
+      <c r="G34" s="316"/>
       <c r="H34" s="219"/>
       <c r="I34" s="145"/>
       <c r="J34" s="145"/>
@@ -8634,22 +8637,22 @@
       <c r="A41" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B41" s="281" t="s">
+      <c r="B41" s="289" t="s">
         <v>898</v>
       </c>
-      <c r="C41" s="282"/>
-      <c r="D41" s="282"/>
-      <c r="E41" s="282"/>
-      <c r="F41" s="282"/>
-      <c r="G41" s="282"/>
-      <c r="H41" s="282"/>
-      <c r="I41" s="282"/>
-      <c r="J41" s="282"/>
-      <c r="K41" s="282"/>
-      <c r="L41" s="282"/>
-      <c r="M41" s="282"/>
-      <c r="N41" s="282"/>
-      <c r="O41" s="283"/>
+      <c r="C41" s="290"/>
+      <c r="D41" s="290"/>
+      <c r="E41" s="290"/>
+      <c r="F41" s="290"/>
+      <c r="G41" s="290"/>
+      <c r="H41" s="290"/>
+      <c r="I41" s="290"/>
+      <c r="J41" s="290"/>
+      <c r="K41" s="290"/>
+      <c r="L41" s="290"/>
+      <c r="M41" s="290"/>
+      <c r="N41" s="290"/>
+      <c r="O41" s="291"/>
       <c r="P41" s="173"/>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.3">
@@ -8657,20 +8660,20 @@
         <f>IF($F$47="convencional","Estrutura + vedação",IF($F$47="não convencional","Paredes de concreto moldado in loco NBR 16055",IF($F$47="inovador","Pré-moldado bloco cerâmico","")))</f>
         <v>Estrutura + vedação</v>
       </c>
-      <c r="B42" s="281"/>
-      <c r="C42" s="282"/>
-      <c r="D42" s="282"/>
-      <c r="E42" s="282"/>
-      <c r="F42" s="282"/>
-      <c r="G42" s="282"/>
-      <c r="H42" s="282"/>
-      <c r="I42" s="282"/>
-      <c r="J42" s="282"/>
-      <c r="K42" s="282"/>
-      <c r="L42" s="282"/>
-      <c r="M42" s="282"/>
-      <c r="N42" s="282"/>
-      <c r="O42" s="283"/>
+      <c r="B42" s="289"/>
+      <c r="C42" s="290"/>
+      <c r="D42" s="290"/>
+      <c r="E42" s="290"/>
+      <c r="F42" s="290"/>
+      <c r="G42" s="290"/>
+      <c r="H42" s="290"/>
+      <c r="I42" s="290"/>
+      <c r="J42" s="290"/>
+      <c r="K42" s="290"/>
+      <c r="L42" s="290"/>
+      <c r="M42" s="290"/>
+      <c r="N42" s="290"/>
+      <c r="O42" s="291"/>
       <c r="P42" s="173"/>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.3">
@@ -8678,20 +8681,20 @@
         <f>IF($F$47="convencional","Alvenaria estrutural",IF($F$47="inovador","Concreto leve",""))</f>
         <v>Alvenaria estrutural</v>
       </c>
-      <c r="B43" s="284"/>
-      <c r="C43" s="285"/>
-      <c r="D43" s="285"/>
-      <c r="E43" s="285"/>
-      <c r="F43" s="285"/>
-      <c r="G43" s="285"/>
-      <c r="H43" s="285"/>
-      <c r="I43" s="285"/>
-      <c r="J43" s="285"/>
-      <c r="K43" s="285"/>
-      <c r="L43" s="285"/>
-      <c r="M43" s="285"/>
-      <c r="N43" s="285"/>
-      <c r="O43" s="286"/>
+      <c r="B43" s="292"/>
+      <c r="C43" s="293"/>
+      <c r="D43" s="293"/>
+      <c r="E43" s="293"/>
+      <c r="F43" s="293"/>
+      <c r="G43" s="293"/>
+      <c r="H43" s="293"/>
+      <c r="I43" s="293"/>
+      <c r="J43" s="293"/>
+      <c r="K43" s="293"/>
+      <c r="L43" s="293"/>
+      <c r="M43" s="293"/>
+      <c r="N43" s="293"/>
+      <c r="O43" s="294"/>
       <c r="P43" s="173"/>
     </row>
     <row r="44" spans="1:16" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3">
@@ -8772,22 +8775,22 @@
       <c r="E47" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F47" s="265" t="s">
+      <c r="F47" s="301" t="s">
         <v>863</v>
       </c>
-      <c r="G47" s="265"/>
+      <c r="G47" s="301"/>
       <c r="H47" s="221"/>
       <c r="I47" s="145"/>
       <c r="J47" s="4" t="s">
         <v>745</v>
       </c>
-      <c r="K47" s="287" t="s">
+      <c r="K47" s="295" t="s">
         <v>864</v>
       </c>
-      <c r="L47" s="287"/>
-      <c r="M47" s="287"/>
-      <c r="N47" s="330"/>
-      <c r="O47" s="330"/>
+      <c r="L47" s="295"/>
+      <c r="M47" s="295"/>
+      <c r="N47" s="251"/>
+      <c r="O47" s="251"/>
       <c r="P47" s="213"/>
     </row>
     <row r="48" spans="1:16" ht="3.15" customHeight="1" x14ac:dyDescent="0.3">
@@ -8902,10 +8905,10 @@
         <v>#VALUE!</v>
       </c>
       <c r="M51" s="176"/>
-      <c r="N51" s="290" t="s">
+      <c r="N51" s="298" t="s">
         <v>67</v>
       </c>
-      <c r="O51" s="290"/>
+      <c r="O51" s="298"/>
       <c r="P51" s="176"/>
       <c r="Q51" s="4"/>
     </row>
@@ -9032,12 +9035,12 @@
       <c r="P56" s="145"/>
     </row>
     <row r="57" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B57" s="267" t="s">
+      <c r="B57" s="303" t="s">
         <v>744</v>
       </c>
-      <c r="C57" s="267"/>
-      <c r="D57" s="267"/>
-      <c r="E57" s="267"/>
+      <c r="C57" s="303"/>
+      <c r="D57" s="303"/>
+      <c r="E57" s="303"/>
       <c r="F57" s="145"/>
       <c r="G57" s="181" t="s">
         <v>26</v>
@@ -9146,58 +9149,58 @@
     </row>
     <row r="62" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="237"/>
-      <c r="B62" s="281" t="s">
+      <c r="B62" s="289" t="s">
         <v>867</v>
       </c>
-      <c r="C62" s="282"/>
-      <c r="D62" s="282"/>
-      <c r="E62" s="282"/>
-      <c r="F62" s="282"/>
-      <c r="G62" s="282"/>
-      <c r="H62" s="282"/>
-      <c r="I62" s="282"/>
-      <c r="J62" s="282"/>
-      <c r="K62" s="282"/>
-      <c r="L62" s="282"/>
-      <c r="M62" s="282"/>
-      <c r="N62" s="282"/>
-      <c r="O62" s="283"/>
+      <c r="C62" s="290"/>
+      <c r="D62" s="290"/>
+      <c r="E62" s="290"/>
+      <c r="F62" s="290"/>
+      <c r="G62" s="290"/>
+      <c r="H62" s="290"/>
+      <c r="I62" s="290"/>
+      <c r="J62" s="290"/>
+      <c r="K62" s="290"/>
+      <c r="L62" s="290"/>
+      <c r="M62" s="290"/>
+      <c r="N62" s="290"/>
+      <c r="O62" s="291"/>
       <c r="P62" s="173"/>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63" s="237"/>
-      <c r="B63" s="281"/>
-      <c r="C63" s="282"/>
-      <c r="D63" s="282"/>
-      <c r="E63" s="282"/>
-      <c r="F63" s="282"/>
-      <c r="G63" s="282"/>
-      <c r="H63" s="282"/>
-      <c r="I63" s="282"/>
-      <c r="J63" s="282"/>
-      <c r="K63" s="282"/>
-      <c r="L63" s="282"/>
-      <c r="M63" s="282"/>
-      <c r="N63" s="282"/>
-      <c r="O63" s="283"/>
+      <c r="B63" s="289"/>
+      <c r="C63" s="290"/>
+      <c r="D63" s="290"/>
+      <c r="E63" s="290"/>
+      <c r="F63" s="290"/>
+      <c r="G63" s="290"/>
+      <c r="H63" s="290"/>
+      <c r="I63" s="290"/>
+      <c r="J63" s="290"/>
+      <c r="K63" s="290"/>
+      <c r="L63" s="290"/>
+      <c r="M63" s="290"/>
+      <c r="N63" s="290"/>
+      <c r="O63" s="291"/>
       <c r="P63" s="173"/>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64" s="237"/>
-      <c r="B64" s="284"/>
-      <c r="C64" s="285"/>
-      <c r="D64" s="285"/>
-      <c r="E64" s="285"/>
-      <c r="F64" s="285"/>
-      <c r="G64" s="285"/>
-      <c r="H64" s="285"/>
-      <c r="I64" s="285"/>
-      <c r="J64" s="285"/>
-      <c r="K64" s="285"/>
-      <c r="L64" s="285"/>
-      <c r="M64" s="285"/>
-      <c r="N64" s="285"/>
-      <c r="O64" s="286"/>
+      <c r="B64" s="292"/>
+      <c r="C64" s="293"/>
+      <c r="D64" s="293"/>
+      <c r="E64" s="293"/>
+      <c r="F64" s="293"/>
+      <c r="G64" s="293"/>
+      <c r="H64" s="293"/>
+      <c r="I64" s="293"/>
+      <c r="J64" s="293"/>
+      <c r="K64" s="293"/>
+      <c r="L64" s="293"/>
+      <c r="M64" s="293"/>
+      <c r="N64" s="293"/>
+      <c r="O64" s="294"/>
       <c r="P64" s="173"/>
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.3">
@@ -9229,10 +9232,10 @@
       <c r="F66" s="145"/>
       <c r="G66" s="145"/>
       <c r="H66" s="145"/>
-      <c r="I66" s="266" t="s">
+      <c r="I66" s="302" t="s">
         <v>893</v>
       </c>
-      <c r="J66" s="266"/>
+      <c r="J66" s="302"/>
       <c r="K66" s="145"/>
       <c r="L66" s="4"/>
       <c r="M66" s="4"/>
@@ -9251,10 +9254,10 @@
       <c r="F67" s="145"/>
       <c r="G67" s="145"/>
       <c r="H67" s="145"/>
-      <c r="I67" s="266" t="s">
+      <c r="I67" s="302" t="s">
         <v>894</v>
       </c>
-      <c r="J67" s="266"/>
+      <c r="J67" s="302"/>
       <c r="K67" s="145"/>
       <c r="L67" s="4"/>
       <c r="M67" s="4"/>
@@ -9267,104 +9270,104 @@
     </row>
     <row r="69" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="237"/>
-      <c r="B69" s="288" t="s">
+      <c r="B69" s="296" t="s">
         <v>698</v>
       </c>
-      <c r="C69" s="261" t="s">
+      <c r="C69" s="252" t="s">
         <v>856</v>
       </c>
-      <c r="D69" s="261" t="s">
+      <c r="D69" s="252" t="s">
         <v>72</v>
       </c>
-      <c r="E69" s="270" t="s">
+      <c r="E69" s="308" t="s">
         <v>71</v>
       </c>
-      <c r="F69" s="271"/>
-      <c r="G69" s="261" t="str">
+      <c r="F69" s="309"/>
+      <c r="G69" s="252" t="str">
         <f>IF(programa=$A$6,"", "Área privativa real
 col. 23")</f>
         <v>Área privativa real
 col. 23</v>
       </c>
-      <c r="H69" s="260" t="s">
+      <c r="H69" s="317" t="s">
         <v>846</v>
       </c>
-      <c r="I69" s="261" t="str">
+      <c r="I69" s="252" t="str">
         <f>IF(programa=$A$6,"","Área privativa equivalente
 col. 24")</f>
         <v>Área privativa equivalente
 col. 24</v>
       </c>
-      <c r="J69" s="261" t="str">
+      <c r="J69" s="252" t="str">
         <f>IF(programa=$A$6,"","Área total real
 col. 37")</f>
         <v>Área total real
 col. 37</v>
       </c>
-      <c r="K69" s="261" t="str">
+      <c r="K69" s="252" t="str">
         <f>IF(programa=$A$6,"Área do lote","Área total equivalente
 col. 38")</f>
         <v>Área total equivalente
 col. 38</v>
       </c>
-      <c r="L69" s="261" t="str">
+      <c r="L69" s="252" t="str">
         <f>IF(programa=$A$6,"","Área equiv. de divisão não proporcional
 col. 30")</f>
         <v>Área equiv. de divisão não proporcional
 col. 30</v>
       </c>
-      <c r="M69" s="261" t="str">
+      <c r="M69" s="252" t="str">
         <f>IF(programa=$A$6,"","Fração Ideal")</f>
         <v>Fração Ideal</v>
       </c>
-      <c r="N69" s="261" t="s">
+      <c r="N69" s="252" t="s">
         <v>748</v>
       </c>
-      <c r="O69" s="261" t="s">
+      <c r="O69" s="252" t="s">
         <v>73</v>
       </c>
-      <c r="P69" s="264"/>
+      <c r="P69" s="314"/>
     </row>
     <row r="70" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="237"/>
-      <c r="B70" s="288"/>
-      <c r="C70" s="261"/>
-      <c r="D70" s="261"/>
-      <c r="E70" s="270"/>
-      <c r="F70" s="271"/>
-      <c r="G70" s="261"/>
-      <c r="H70" s="260"/>
-      <c r="I70" s="261"/>
-      <c r="J70" s="261"/>
-      <c r="K70" s="261"/>
-      <c r="L70" s="261"/>
-      <c r="M70" s="261"/>
-      <c r="N70" s="261"/>
-      <c r="O70" s="261"/>
-      <c r="P70" s="264"/>
+      <c r="B70" s="296"/>
+      <c r="C70" s="252"/>
+      <c r="D70" s="252"/>
+      <c r="E70" s="308"/>
+      <c r="F70" s="309"/>
+      <c r="G70" s="252"/>
+      <c r="H70" s="317"/>
+      <c r="I70" s="252"/>
+      <c r="J70" s="252"/>
+      <c r="K70" s="252"/>
+      <c r="L70" s="252"/>
+      <c r="M70" s="252"/>
+      <c r="N70" s="252"/>
+      <c r="O70" s="252"/>
+      <c r="P70" s="314"/>
     </row>
     <row r="71" spans="1:16" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="237"/>
-      <c r="B71" s="289"/>
-      <c r="C71" s="262"/>
-      <c r="D71" s="262"/>
-      <c r="E71" s="272"/>
-      <c r="F71" s="273"/>
-      <c r="G71" s="262"/>
+      <c r="B71" s="297"/>
+      <c r="C71" s="253"/>
+      <c r="D71" s="253"/>
+      <c r="E71" s="310"/>
+      <c r="F71" s="311"/>
+      <c r="G71" s="253"/>
       <c r="H71" s="220" t="s">
         <v>847</v>
       </c>
-      <c r="I71" s="262"/>
-      <c r="J71" s="262"/>
-      <c r="K71" s="262"/>
-      <c r="L71" s="262"/>
-      <c r="M71" s="262"/>
-      <c r="N71" s="262"/>
-      <c r="O71" s="262"/>
-      <c r="P71" s="264"/>
+      <c r="I71" s="253"/>
+      <c r="J71" s="253"/>
+      <c r="K71" s="253"/>
+      <c r="L71" s="253"/>
+      <c r="M71" s="253"/>
+      <c r="N71" s="253"/>
+      <c r="O71" s="253"/>
+      <c r="P71" s="314"/>
     </row>
     <row r="72" spans="1:16" ht="60.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="245" t="s">
+      <c r="A72" s="330" t="s">
         <v>70</v>
       </c>
       <c r="B72" s="114">
@@ -9374,10 +9377,10 @@
       <c r="D72" s="223" t="s">
         <v>892</v>
       </c>
-      <c r="E72" s="257" t="s">
+      <c r="E72" s="312" t="s">
         <v>866</v>
       </c>
-      <c r="F72" s="258"/>
+      <c r="F72" s="313"/>
       <c r="G72" s="224">
         <v>257.7</v>
       </c>
@@ -9409,15 +9412,15 @@
       <c r="P72" s="16"/>
     </row>
     <row r="73" spans="1:16" ht="60.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="245"/>
+      <c r="A73" s="330"/>
       <c r="B73" s="114">
         <f>B72+1</f>
         <v>2</v>
       </c>
       <c r="C73" s="114"/>
       <c r="D73" s="223"/>
-      <c r="E73" s="257"/>
-      <c r="F73" s="258"/>
+      <c r="E73" s="312"/>
+      <c r="F73" s="313"/>
       <c r="G73" s="224"/>
       <c r="H73" s="224"/>
       <c r="I73" s="228"/>
@@ -9433,15 +9436,15 @@
       <c r="P73" s="16"/>
     </row>
     <row r="74" spans="1:16" ht="60.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="245"/>
+      <c r="A74" s="330"/>
       <c r="B74" s="114">
         <f t="shared" ref="B74:B171" si="1">B73+1</f>
         <v>3</v>
       </c>
       <c r="C74" s="114"/>
       <c r="D74" s="223"/>
-      <c r="E74" s="257"/>
-      <c r="F74" s="258"/>
+      <c r="E74" s="312"/>
+      <c r="F74" s="313"/>
       <c r="G74" s="224"/>
       <c r="H74" s="224"/>
       <c r="I74" s="228"/>
@@ -9457,15 +9460,15 @@
       <c r="P74" s="16"/>
     </row>
     <row r="75" spans="1:16" ht="60.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="245"/>
+      <c r="A75" s="330"/>
       <c r="B75" s="114">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="C75" s="114"/>
       <c r="D75" s="223"/>
-      <c r="E75" s="257"/>
-      <c r="F75" s="258"/>
+      <c r="E75" s="312"/>
+      <c r="F75" s="313"/>
       <c r="G75" s="228"/>
       <c r="H75" s="228"/>
       <c r="I75" s="228"/>
@@ -9481,15 +9484,15 @@
       <c r="P75" s="16"/>
     </row>
     <row r="76" spans="1:16" ht="60.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="245"/>
+      <c r="A76" s="330"/>
       <c r="B76" s="114">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="C76" s="114"/>
       <c r="D76" s="223"/>
-      <c r="E76" s="257"/>
-      <c r="F76" s="258"/>
+      <c r="E76" s="312"/>
+      <c r="F76" s="313"/>
       <c r="G76" s="228"/>
       <c r="H76" s="228"/>
       <c r="I76" s="228"/>
@@ -9505,15 +9508,15 @@
       <c r="P76" s="16"/>
     </row>
     <row r="77" spans="1:16" ht="60.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="245"/>
+      <c r="A77" s="330"/>
       <c r="B77" s="114">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="C77" s="114"/>
       <c r="D77" s="223"/>
-      <c r="E77" s="257"/>
-      <c r="F77" s="258"/>
+      <c r="E77" s="312"/>
+      <c r="F77" s="313"/>
       <c r="G77" s="228"/>
       <c r="H77" s="228"/>
       <c r="I77" s="228"/>
@@ -9529,15 +9532,15 @@
       <c r="P77" s="16"/>
     </row>
     <row r="78" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="245"/>
+      <c r="A78" s="330"/>
       <c r="B78" s="114">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="C78" s="114"/>
       <c r="D78" s="227"/>
-      <c r="E78" s="242"/>
-      <c r="F78" s="243"/>
+      <c r="E78" s="306"/>
+      <c r="F78" s="307"/>
       <c r="G78" s="228"/>
       <c r="H78" s="228"/>
       <c r="I78" s="228"/>
@@ -9553,15 +9556,15 @@
       <c r="P78" s="16"/>
     </row>
     <row r="79" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="245"/>
+      <c r="A79" s="330"/>
       <c r="B79" s="114">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="C79" s="114"/>
       <c r="D79" s="227"/>
-      <c r="E79" s="242"/>
-      <c r="F79" s="243"/>
+      <c r="E79" s="306"/>
+      <c r="F79" s="307"/>
       <c r="G79" s="228"/>
       <c r="H79" s="228"/>
       <c r="I79" s="228"/>
@@ -9577,15 +9580,15 @@
       <c r="P79" s="16"/>
     </row>
     <row r="80" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="245"/>
+      <c r="A80" s="330"/>
       <c r="B80" s="114">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="C80" s="114"/>
       <c r="D80" s="227"/>
-      <c r="E80" s="242"/>
-      <c r="F80" s="243"/>
+      <c r="E80" s="306"/>
+      <c r="F80" s="307"/>
       <c r="G80" s="228"/>
       <c r="H80" s="228"/>
       <c r="I80" s="228"/>
@@ -9601,15 +9604,15 @@
       <c r="P80" s="16"/>
     </row>
     <row r="81" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="245"/>
+      <c r="A81" s="330"/>
       <c r="B81" s="114">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="C81" s="114"/>
       <c r="D81" s="227"/>
-      <c r="E81" s="242"/>
-      <c r="F81" s="243"/>
+      <c r="E81" s="306"/>
+      <c r="F81" s="307"/>
       <c r="G81" s="228"/>
       <c r="H81" s="228"/>
       <c r="I81" s="228"/>
@@ -9625,15 +9628,15 @@
       <c r="P81" s="16"/>
     </row>
     <row r="82" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="245"/>
+      <c r="A82" s="330"/>
       <c r="B82" s="114">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
       <c r="C82" s="114"/>
       <c r="D82" s="227"/>
-      <c r="E82" s="242"/>
-      <c r="F82" s="243"/>
+      <c r="E82" s="306"/>
+      <c r="F82" s="307"/>
       <c r="G82" s="228"/>
       <c r="H82" s="228"/>
       <c r="I82" s="228"/>
@@ -9649,15 +9652,15 @@
       <c r="P82" s="16"/>
     </row>
     <row r="83" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="245"/>
+      <c r="A83" s="330"/>
       <c r="B83" s="114">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="C83" s="114"/>
       <c r="D83" s="227"/>
-      <c r="E83" s="242"/>
-      <c r="F83" s="243"/>
+      <c r="E83" s="306"/>
+      <c r="F83" s="307"/>
       <c r="G83" s="228"/>
       <c r="H83" s="228"/>
       <c r="I83" s="228"/>
@@ -9673,15 +9676,15 @@
       <c r="P83" s="16"/>
     </row>
     <row r="84" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="245"/>
+      <c r="A84" s="330"/>
       <c r="B84" s="114">
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="C84" s="114"/>
       <c r="D84" s="227"/>
-      <c r="E84" s="242"/>
-      <c r="F84" s="243"/>
+      <c r="E84" s="306"/>
+      <c r="F84" s="307"/>
       <c r="G84" s="228"/>
       <c r="H84" s="228"/>
       <c r="I84" s="228"/>
@@ -9697,15 +9700,15 @@
       <c r="P84" s="16"/>
     </row>
     <row r="85" spans="1:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="245"/>
+      <c r="A85" s="330"/>
       <c r="B85" s="114">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="C85" s="114"/>
       <c r="D85" s="227"/>
-      <c r="E85" s="242"/>
-      <c r="F85" s="243"/>
+      <c r="E85" s="306"/>
+      <c r="F85" s="307"/>
       <c r="G85" s="228"/>
       <c r="H85" s="228"/>
       <c r="I85" s="228"/>
@@ -9721,15 +9724,15 @@
       <c r="P85" s="16"/>
     </row>
     <row r="86" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="245"/>
+      <c r="A86" s="330"/>
       <c r="B86" s="114">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="C86" s="114"/>
       <c r="D86" s="227"/>
-      <c r="E86" s="242"/>
-      <c r="F86" s="243"/>
+      <c r="E86" s="306"/>
+      <c r="F86" s="307"/>
       <c r="G86" s="228"/>
       <c r="H86" s="228"/>
       <c r="I86" s="228"/>
@@ -9745,15 +9748,15 @@
       <c r="P86" s="16"/>
     </row>
     <row r="87" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="245"/>
+      <c r="A87" s="330"/>
       <c r="B87" s="114">
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
       <c r="C87" s="114"/>
       <c r="D87" s="227"/>
-      <c r="E87" s="242"/>
-      <c r="F87" s="243"/>
+      <c r="E87" s="306"/>
+      <c r="F87" s="307"/>
       <c r="G87" s="228"/>
       <c r="H87" s="228"/>
       <c r="I87" s="228"/>
@@ -9769,15 +9772,15 @@
       <c r="P87" s="16"/>
     </row>
     <row r="88" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="245"/>
+      <c r="A88" s="330"/>
       <c r="B88" s="114">
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
       <c r="C88" s="114"/>
       <c r="D88" s="227"/>
-      <c r="E88" s="242"/>
-      <c r="F88" s="243"/>
+      <c r="E88" s="306"/>
+      <c r="F88" s="307"/>
       <c r="G88" s="228"/>
       <c r="H88" s="228"/>
       <c r="I88" s="228"/>
@@ -9793,15 +9796,15 @@
       <c r="P88" s="16"/>
     </row>
     <row r="89" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="245"/>
+      <c r="A89" s="330"/>
       <c r="B89" s="114">
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="C89" s="114"/>
       <c r="D89" s="227"/>
-      <c r="E89" s="242"/>
-      <c r="F89" s="243"/>
+      <c r="E89" s="306"/>
+      <c r="F89" s="307"/>
       <c r="G89" s="228"/>
       <c r="H89" s="228"/>
       <c r="I89" s="228"/>
@@ -9817,15 +9820,15 @@
       <c r="P89" s="16"/>
     </row>
     <row r="90" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="245"/>
+      <c r="A90" s="330"/>
       <c r="B90" s="114">
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="C90" s="114"/>
       <c r="D90" s="227"/>
-      <c r="E90" s="242"/>
-      <c r="F90" s="243"/>
+      <c r="E90" s="306"/>
+      <c r="F90" s="307"/>
       <c r="G90" s="228"/>
       <c r="H90" s="228"/>
       <c r="I90" s="228"/>
@@ -9841,15 +9844,15 @@
       <c r="P90" s="16"/>
     </row>
     <row r="91" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="245"/>
+      <c r="A91" s="330"/>
       <c r="B91" s="114">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="C91" s="114"/>
       <c r="D91" s="227"/>
-      <c r="E91" s="242"/>
-      <c r="F91" s="243"/>
+      <c r="E91" s="306"/>
+      <c r="F91" s="307"/>
       <c r="G91" s="228"/>
       <c r="H91" s="228"/>
       <c r="I91" s="228"/>
@@ -9872,8 +9875,8 @@
       </c>
       <c r="C92" s="114"/>
       <c r="D92" s="227"/>
-      <c r="E92" s="242"/>
-      <c r="F92" s="243"/>
+      <c r="E92" s="306"/>
+      <c r="F92" s="307"/>
       <c r="G92" s="228"/>
       <c r="H92" s="228"/>
       <c r="I92" s="228"/>
@@ -9896,8 +9899,8 @@
       </c>
       <c r="C93" s="114"/>
       <c r="D93" s="227"/>
-      <c r="E93" s="242"/>
-      <c r="F93" s="243"/>
+      <c r="E93" s="306"/>
+      <c r="F93" s="307"/>
       <c r="G93" s="228"/>
       <c r="H93" s="228"/>
       <c r="I93" s="228"/>
@@ -9920,8 +9923,8 @@
       </c>
       <c r="C94" s="114"/>
       <c r="D94" s="227"/>
-      <c r="E94" s="242"/>
-      <c r="F94" s="243"/>
+      <c r="E94" s="306"/>
+      <c r="F94" s="307"/>
       <c r="G94" s="228"/>
       <c r="H94" s="228"/>
       <c r="I94" s="228"/>
@@ -9944,8 +9947,8 @@
       </c>
       <c r="C95" s="114"/>
       <c r="D95" s="227"/>
-      <c r="E95" s="242"/>
-      <c r="F95" s="243"/>
+      <c r="E95" s="306"/>
+      <c r="F95" s="307"/>
       <c r="G95" s="228"/>
       <c r="H95" s="228"/>
       <c r="I95" s="228"/>
@@ -9968,8 +9971,8 @@
       </c>
       <c r="C96" s="114"/>
       <c r="D96" s="227"/>
-      <c r="E96" s="242"/>
-      <c r="F96" s="243"/>
+      <c r="E96" s="306"/>
+      <c r="F96" s="307"/>
       <c r="G96" s="228"/>
       <c r="H96" s="228"/>
       <c r="I96" s="228"/>
@@ -9992,8 +9995,8 @@
       </c>
       <c r="C97" s="114"/>
       <c r="D97" s="227"/>
-      <c r="E97" s="242"/>
-      <c r="F97" s="243"/>
+      <c r="E97" s="306"/>
+      <c r="F97" s="307"/>
       <c r="G97" s="228"/>
       <c r="H97" s="228"/>
       <c r="I97" s="228"/>
@@ -10016,8 +10019,8 @@
       </c>
       <c r="C98" s="114"/>
       <c r="D98" s="227"/>
-      <c r="E98" s="242"/>
-      <c r="F98" s="243"/>
+      <c r="E98" s="306"/>
+      <c r="F98" s="307"/>
       <c r="G98" s="228"/>
       <c r="H98" s="228"/>
       <c r="I98" s="228"/>
@@ -10040,8 +10043,8 @@
       </c>
       <c r="C99" s="114"/>
       <c r="D99" s="227"/>
-      <c r="E99" s="242"/>
-      <c r="F99" s="243"/>
+      <c r="E99" s="306"/>
+      <c r="F99" s="307"/>
       <c r="G99" s="228"/>
       <c r="H99" s="228"/>
       <c r="I99" s="228"/>
@@ -10064,8 +10067,8 @@
       </c>
       <c r="C100" s="114"/>
       <c r="D100" s="227"/>
-      <c r="E100" s="242"/>
-      <c r="F100" s="243"/>
+      <c r="E100" s="306"/>
+      <c r="F100" s="307"/>
       <c r="G100" s="228"/>
       <c r="H100" s="228"/>
       <c r="I100" s="228"/>
@@ -10088,8 +10091,8 @@
       </c>
       <c r="C101" s="114"/>
       <c r="D101" s="227"/>
-      <c r="E101" s="242"/>
-      <c r="F101" s="243"/>
+      <c r="E101" s="306"/>
+      <c r="F101" s="307"/>
       <c r="G101" s="228"/>
       <c r="H101" s="228"/>
       <c r="I101" s="228"/>
@@ -10112,8 +10115,8 @@
       </c>
       <c r="C102" s="114"/>
       <c r="D102" s="227"/>
-      <c r="E102" s="242"/>
-      <c r="F102" s="243"/>
+      <c r="E102" s="306"/>
+      <c r="F102" s="307"/>
       <c r="G102" s="228"/>
       <c r="H102" s="228"/>
       <c r="I102" s="228"/>
@@ -10136,8 +10139,8 @@
       </c>
       <c r="C103" s="114"/>
       <c r="D103" s="227"/>
-      <c r="E103" s="242"/>
-      <c r="F103" s="243"/>
+      <c r="E103" s="306"/>
+      <c r="F103" s="307"/>
       <c r="G103" s="228"/>
       <c r="H103" s="228"/>
       <c r="I103" s="228"/>
@@ -10160,8 +10163,8 @@
       </c>
       <c r="C104" s="114"/>
       <c r="D104" s="227"/>
-      <c r="E104" s="242"/>
-      <c r="F104" s="243"/>
+      <c r="E104" s="306"/>
+      <c r="F104" s="307"/>
       <c r="G104" s="228"/>
       <c r="H104" s="228"/>
       <c r="I104" s="228"/>
@@ -10184,8 +10187,8 @@
       </c>
       <c r="C105" s="114"/>
       <c r="D105" s="227"/>
-      <c r="E105" s="242"/>
-      <c r="F105" s="243"/>
+      <c r="E105" s="306"/>
+      <c r="F105" s="307"/>
       <c r="G105" s="228"/>
       <c r="H105" s="228"/>
       <c r="I105" s="228"/>
@@ -10208,8 +10211,8 @@
       </c>
       <c r="C106" s="114"/>
       <c r="D106" s="227"/>
-      <c r="E106" s="242"/>
-      <c r="F106" s="243"/>
+      <c r="E106" s="306"/>
+      <c r="F106" s="307"/>
       <c r="G106" s="228"/>
       <c r="H106" s="228"/>
       <c r="I106" s="228"/>
@@ -10232,8 +10235,8 @@
       </c>
       <c r="C107" s="114"/>
       <c r="D107" s="227"/>
-      <c r="E107" s="242"/>
-      <c r="F107" s="243"/>
+      <c r="E107" s="306"/>
+      <c r="F107" s="307"/>
       <c r="G107" s="228"/>
       <c r="H107" s="228"/>
       <c r="I107" s="228"/>
@@ -10256,8 +10259,8 @@
       </c>
       <c r="C108" s="114"/>
       <c r="D108" s="227"/>
-      <c r="E108" s="242"/>
-      <c r="F108" s="243"/>
+      <c r="E108" s="306"/>
+      <c r="F108" s="307"/>
       <c r="G108" s="228"/>
       <c r="H108" s="228"/>
       <c r="I108" s="228"/>
@@ -10280,8 +10283,8 @@
       </c>
       <c r="C109" s="114"/>
       <c r="D109" s="227"/>
-      <c r="E109" s="242"/>
-      <c r="F109" s="243"/>
+      <c r="E109" s="306"/>
+      <c r="F109" s="307"/>
       <c r="G109" s="228"/>
       <c r="H109" s="228"/>
       <c r="I109" s="228"/>
@@ -10304,8 +10307,8 @@
       </c>
       <c r="C110" s="114"/>
       <c r="D110" s="227"/>
-      <c r="E110" s="242"/>
-      <c r="F110" s="243"/>
+      <c r="E110" s="306"/>
+      <c r="F110" s="307"/>
       <c r="G110" s="228"/>
       <c r="H110" s="228"/>
       <c r="I110" s="228"/>
@@ -10328,8 +10331,8 @@
       </c>
       <c r="C111" s="114"/>
       <c r="D111" s="227"/>
-      <c r="E111" s="242"/>
-      <c r="F111" s="243"/>
+      <c r="E111" s="306"/>
+      <c r="F111" s="307"/>
       <c r="G111" s="228"/>
       <c r="H111" s="228"/>
       <c r="I111" s="228"/>
@@ -10352,8 +10355,8 @@
       </c>
       <c r="C112" s="114"/>
       <c r="D112" s="227"/>
-      <c r="E112" s="242"/>
-      <c r="F112" s="243"/>
+      <c r="E112" s="306"/>
+      <c r="F112" s="307"/>
       <c r="G112" s="228"/>
       <c r="H112" s="228"/>
       <c r="I112" s="228"/>
@@ -10376,8 +10379,8 @@
       </c>
       <c r="C113" s="114"/>
       <c r="D113" s="227"/>
-      <c r="E113" s="242"/>
-      <c r="F113" s="243"/>
+      <c r="E113" s="306"/>
+      <c r="F113" s="307"/>
       <c r="G113" s="228"/>
       <c r="H113" s="228"/>
       <c r="I113" s="228"/>
@@ -10400,8 +10403,8 @@
       </c>
       <c r="C114" s="114"/>
       <c r="D114" s="227"/>
-      <c r="E114" s="242"/>
-      <c r="F114" s="243"/>
+      <c r="E114" s="306"/>
+      <c r="F114" s="307"/>
       <c r="G114" s="228"/>
       <c r="H114" s="228"/>
       <c r="I114" s="228"/>
@@ -10424,8 +10427,8 @@
       </c>
       <c r="C115" s="114"/>
       <c r="D115" s="227"/>
-      <c r="E115" s="242"/>
-      <c r="F115" s="243"/>
+      <c r="E115" s="306"/>
+      <c r="F115" s="307"/>
       <c r="G115" s="228"/>
       <c r="H115" s="228"/>
       <c r="I115" s="228"/>
@@ -10448,8 +10451,8 @@
       </c>
       <c r="C116" s="114"/>
       <c r="D116" s="227"/>
-      <c r="E116" s="242"/>
-      <c r="F116" s="243"/>
+      <c r="E116" s="306"/>
+      <c r="F116" s="307"/>
       <c r="G116" s="228"/>
       <c r="H116" s="228"/>
       <c r="I116" s="228"/>
@@ -10472,8 +10475,8 @@
       </c>
       <c r="C117" s="114"/>
       <c r="D117" s="227"/>
-      <c r="E117" s="242"/>
-      <c r="F117" s="243"/>
+      <c r="E117" s="306"/>
+      <c r="F117" s="307"/>
       <c r="G117" s="228"/>
       <c r="H117" s="228"/>
       <c r="I117" s="228"/>
@@ -10496,8 +10499,8 @@
       </c>
       <c r="C118" s="114"/>
       <c r="D118" s="227"/>
-      <c r="E118" s="242"/>
-      <c r="F118" s="243"/>
+      <c r="E118" s="306"/>
+      <c r="F118" s="307"/>
       <c r="G118" s="228"/>
       <c r="H118" s="228"/>
       <c r="I118" s="228"/>
@@ -10520,8 +10523,8 @@
       </c>
       <c r="C119" s="114"/>
       <c r="D119" s="227"/>
-      <c r="E119" s="242"/>
-      <c r="F119" s="243"/>
+      <c r="E119" s="306"/>
+      <c r="F119" s="307"/>
       <c r="G119" s="228"/>
       <c r="H119" s="228"/>
       <c r="I119" s="228"/>
@@ -10544,8 +10547,8 @@
       </c>
       <c r="C120" s="114"/>
       <c r="D120" s="227"/>
-      <c r="E120" s="242"/>
-      <c r="F120" s="243"/>
+      <c r="E120" s="306"/>
+      <c r="F120" s="307"/>
       <c r="G120" s="228"/>
       <c r="H120" s="228"/>
       <c r="I120" s="228"/>
@@ -10568,8 +10571,8 @@
       </c>
       <c r="C121" s="114"/>
       <c r="D121" s="227"/>
-      <c r="E121" s="242"/>
-      <c r="F121" s="243"/>
+      <c r="E121" s="306"/>
+      <c r="F121" s="307"/>
       <c r="G121" s="228"/>
       <c r="H121" s="228"/>
       <c r="I121" s="228"/>
@@ -10592,8 +10595,8 @@
       </c>
       <c r="C122" s="114"/>
       <c r="D122" s="227"/>
-      <c r="E122" s="242"/>
-      <c r="F122" s="243"/>
+      <c r="E122" s="306"/>
+      <c r="F122" s="307"/>
       <c r="G122" s="228"/>
       <c r="H122" s="228"/>
       <c r="I122" s="228"/>
@@ -10616,8 +10619,8 @@
       </c>
       <c r="C123" s="114"/>
       <c r="D123" s="227"/>
-      <c r="E123" s="242"/>
-      <c r="F123" s="243"/>
+      <c r="E123" s="306"/>
+      <c r="F123" s="307"/>
       <c r="G123" s="228"/>
       <c r="H123" s="228"/>
       <c r="I123" s="228"/>
@@ -10640,8 +10643,8 @@
       </c>
       <c r="C124" s="114"/>
       <c r="D124" s="227"/>
-      <c r="E124" s="242"/>
-      <c r="F124" s="243"/>
+      <c r="E124" s="306"/>
+      <c r="F124" s="307"/>
       <c r="G124" s="228"/>
       <c r="H124" s="228"/>
       <c r="I124" s="228"/>
@@ -10664,8 +10667,8 @@
       </c>
       <c r="C125" s="114"/>
       <c r="D125" s="227"/>
-      <c r="E125" s="242"/>
-      <c r="F125" s="243"/>
+      <c r="E125" s="306"/>
+      <c r="F125" s="307"/>
       <c r="G125" s="228"/>
       <c r="H125" s="228"/>
       <c r="I125" s="228"/>
@@ -10688,8 +10691,8 @@
       </c>
       <c r="C126" s="114"/>
       <c r="D126" s="227"/>
-      <c r="E126" s="242"/>
-      <c r="F126" s="243"/>
+      <c r="E126" s="306"/>
+      <c r="F126" s="307"/>
       <c r="G126" s="228"/>
       <c r="H126" s="228"/>
       <c r="I126" s="228"/>
@@ -10712,8 +10715,8 @@
       </c>
       <c r="C127" s="114"/>
       <c r="D127" s="227"/>
-      <c r="E127" s="242"/>
-      <c r="F127" s="243"/>
+      <c r="E127" s="306"/>
+      <c r="F127" s="307"/>
       <c r="G127" s="228"/>
       <c r="H127" s="228"/>
       <c r="I127" s="228"/>
@@ -10736,8 +10739,8 @@
       </c>
       <c r="C128" s="114"/>
       <c r="D128" s="227"/>
-      <c r="E128" s="242"/>
-      <c r="F128" s="243"/>
+      <c r="E128" s="306"/>
+      <c r="F128" s="307"/>
       <c r="G128" s="228"/>
       <c r="H128" s="228"/>
       <c r="I128" s="228"/>
@@ -10760,8 +10763,8 @@
       </c>
       <c r="C129" s="114"/>
       <c r="D129" s="227"/>
-      <c r="E129" s="242"/>
-      <c r="F129" s="243"/>
+      <c r="E129" s="306"/>
+      <c r="F129" s="307"/>
       <c r="G129" s="228"/>
       <c r="H129" s="228"/>
       <c r="I129" s="228"/>
@@ -10784,8 +10787,8 @@
       </c>
       <c r="C130" s="114"/>
       <c r="D130" s="227"/>
-      <c r="E130" s="242"/>
-      <c r="F130" s="243"/>
+      <c r="E130" s="306"/>
+      <c r="F130" s="307"/>
       <c r="G130" s="228"/>
       <c r="H130" s="228"/>
       <c r="I130" s="228"/>
@@ -10808,8 +10811,8 @@
       </c>
       <c r="C131" s="114"/>
       <c r="D131" s="227"/>
-      <c r="E131" s="242"/>
-      <c r="F131" s="243"/>
+      <c r="E131" s="306"/>
+      <c r="F131" s="307"/>
       <c r="G131" s="228"/>
       <c r="H131" s="228"/>
       <c r="I131" s="228"/>
@@ -10832,8 +10835,8 @@
       </c>
       <c r="C132" s="114"/>
       <c r="D132" s="227"/>
-      <c r="E132" s="242"/>
-      <c r="F132" s="243"/>
+      <c r="E132" s="306"/>
+      <c r="F132" s="307"/>
       <c r="G132" s="228"/>
       <c r="H132" s="228"/>
       <c r="I132" s="228"/>
@@ -10856,8 +10859,8 @@
       </c>
       <c r="C133" s="114"/>
       <c r="D133" s="227"/>
-      <c r="E133" s="242"/>
-      <c r="F133" s="243"/>
+      <c r="E133" s="306"/>
+      <c r="F133" s="307"/>
       <c r="G133" s="228"/>
       <c r="H133" s="228"/>
       <c r="I133" s="228"/>
@@ -10880,8 +10883,8 @@
       </c>
       <c r="C134" s="114"/>
       <c r="D134" s="227"/>
-      <c r="E134" s="242"/>
-      <c r="F134" s="243"/>
+      <c r="E134" s="306"/>
+      <c r="F134" s="307"/>
       <c r="G134" s="228"/>
       <c r="H134" s="228"/>
       <c r="I134" s="228"/>
@@ -10904,8 +10907,8 @@
       </c>
       <c r="C135" s="114"/>
       <c r="D135" s="227"/>
-      <c r="E135" s="242"/>
-      <c r="F135" s="243"/>
+      <c r="E135" s="306"/>
+      <c r="F135" s="307"/>
       <c r="G135" s="228"/>
       <c r="H135" s="228"/>
       <c r="I135" s="228"/>
@@ -10928,8 +10931,8 @@
       </c>
       <c r="C136" s="114"/>
       <c r="D136" s="227"/>
-      <c r="E136" s="242"/>
-      <c r="F136" s="243"/>
+      <c r="E136" s="306"/>
+      <c r="F136" s="307"/>
       <c r="G136" s="228"/>
       <c r="H136" s="228"/>
       <c r="I136" s="228"/>
@@ -10952,8 +10955,8 @@
       </c>
       <c r="C137" s="114"/>
       <c r="D137" s="227"/>
-      <c r="E137" s="242"/>
-      <c r="F137" s="243"/>
+      <c r="E137" s="306"/>
+      <c r="F137" s="307"/>
       <c r="G137" s="228"/>
       <c r="H137" s="228"/>
       <c r="I137" s="228"/>
@@ -10976,8 +10979,8 @@
       </c>
       <c r="C138" s="114"/>
       <c r="D138" s="227"/>
-      <c r="E138" s="242"/>
-      <c r="F138" s="243"/>
+      <c r="E138" s="306"/>
+      <c r="F138" s="307"/>
       <c r="G138" s="228"/>
       <c r="H138" s="228"/>
       <c r="I138" s="228"/>
@@ -11000,8 +11003,8 @@
       </c>
       <c r="C139" s="114"/>
       <c r="D139" s="227"/>
-      <c r="E139" s="242"/>
-      <c r="F139" s="243"/>
+      <c r="E139" s="306"/>
+      <c r="F139" s="307"/>
       <c r="G139" s="228"/>
       <c r="H139" s="228"/>
       <c r="I139" s="228"/>
@@ -11024,8 +11027,8 @@
       </c>
       <c r="C140" s="114"/>
       <c r="D140" s="227"/>
-      <c r="E140" s="242"/>
-      <c r="F140" s="243"/>
+      <c r="E140" s="306"/>
+      <c r="F140" s="307"/>
       <c r="G140" s="228"/>
       <c r="H140" s="228"/>
       <c r="I140" s="228"/>
@@ -11048,8 +11051,8 @@
       </c>
       <c r="C141" s="114"/>
       <c r="D141" s="227"/>
-      <c r="E141" s="242"/>
-      <c r="F141" s="243"/>
+      <c r="E141" s="306"/>
+      <c r="F141" s="307"/>
       <c r="G141" s="228"/>
       <c r="H141" s="228"/>
       <c r="I141" s="228"/>
@@ -11072,8 +11075,8 @@
       </c>
       <c r="C142" s="114"/>
       <c r="D142" s="227"/>
-      <c r="E142" s="242"/>
-      <c r="F142" s="243"/>
+      <c r="E142" s="306"/>
+      <c r="F142" s="307"/>
       <c r="G142" s="228"/>
       <c r="H142" s="228"/>
       <c r="I142" s="228"/>
@@ -11096,8 +11099,8 @@
       </c>
       <c r="C143" s="114"/>
       <c r="D143" s="227"/>
-      <c r="E143" s="242"/>
-      <c r="F143" s="243"/>
+      <c r="E143" s="306"/>
+      <c r="F143" s="307"/>
       <c r="G143" s="228"/>
       <c r="H143" s="228"/>
       <c r="I143" s="228"/>
@@ -11120,8 +11123,8 @@
       </c>
       <c r="C144" s="114"/>
       <c r="D144" s="227"/>
-      <c r="E144" s="242"/>
-      <c r="F144" s="243"/>
+      <c r="E144" s="306"/>
+      <c r="F144" s="307"/>
       <c r="G144" s="228"/>
       <c r="H144" s="228"/>
       <c r="I144" s="228"/>
@@ -11144,8 +11147,8 @@
       </c>
       <c r="C145" s="114"/>
       <c r="D145" s="227"/>
-      <c r="E145" s="242"/>
-      <c r="F145" s="243"/>
+      <c r="E145" s="306"/>
+      <c r="F145" s="307"/>
       <c r="G145" s="228"/>
       <c r="H145" s="228"/>
       <c r="I145" s="228"/>
@@ -11168,8 +11171,8 @@
       </c>
       <c r="C146" s="114"/>
       <c r="D146" s="227"/>
-      <c r="E146" s="242"/>
-      <c r="F146" s="243"/>
+      <c r="E146" s="306"/>
+      <c r="F146" s="307"/>
       <c r="G146" s="228"/>
       <c r="H146" s="228"/>
       <c r="I146" s="228"/>
@@ -11192,8 +11195,8 @@
       </c>
       <c r="C147" s="114"/>
       <c r="D147" s="227"/>
-      <c r="E147" s="242"/>
-      <c r="F147" s="243"/>
+      <c r="E147" s="306"/>
+      <c r="F147" s="307"/>
       <c r="G147" s="228"/>
       <c r="H147" s="228"/>
       <c r="I147" s="228"/>
@@ -11216,8 +11219,8 @@
       </c>
       <c r="C148" s="114"/>
       <c r="D148" s="227"/>
-      <c r="E148" s="242"/>
-      <c r="F148" s="243"/>
+      <c r="E148" s="306"/>
+      <c r="F148" s="307"/>
       <c r="G148" s="228"/>
       <c r="H148" s="228"/>
       <c r="I148" s="228"/>
@@ -11240,8 +11243,8 @@
       </c>
       <c r="C149" s="114"/>
       <c r="D149" s="227"/>
-      <c r="E149" s="242"/>
-      <c r="F149" s="243"/>
+      <c r="E149" s="306"/>
+      <c r="F149" s="307"/>
       <c r="G149" s="228"/>
       <c r="H149" s="228"/>
       <c r="I149" s="228"/>
@@ -11264,8 +11267,8 @@
       </c>
       <c r="C150" s="114"/>
       <c r="D150" s="227"/>
-      <c r="E150" s="242"/>
-      <c r="F150" s="243"/>
+      <c r="E150" s="306"/>
+      <c r="F150" s="307"/>
       <c r="G150" s="228"/>
       <c r="H150" s="228"/>
       <c r="I150" s="228"/>
@@ -11288,8 +11291,8 @@
       </c>
       <c r="C151" s="114"/>
       <c r="D151" s="227"/>
-      <c r="E151" s="242"/>
-      <c r="F151" s="243"/>
+      <c r="E151" s="306"/>
+      <c r="F151" s="307"/>
       <c r="G151" s="228"/>
       <c r="H151" s="228"/>
       <c r="I151" s="228"/>
@@ -11312,8 +11315,8 @@
       </c>
       <c r="C152" s="114"/>
       <c r="D152" s="227"/>
-      <c r="E152" s="242"/>
-      <c r="F152" s="243"/>
+      <c r="E152" s="306"/>
+      <c r="F152" s="307"/>
       <c r="G152" s="228"/>
       <c r="H152" s="228"/>
       <c r="I152" s="228"/>
@@ -11336,8 +11339,8 @@
       </c>
       <c r="C153" s="114"/>
       <c r="D153" s="227"/>
-      <c r="E153" s="242"/>
-      <c r="F153" s="243"/>
+      <c r="E153" s="306"/>
+      <c r="F153" s="307"/>
       <c r="G153" s="228"/>
       <c r="H153" s="228"/>
       <c r="I153" s="228"/>
@@ -11360,8 +11363,8 @@
       </c>
       <c r="C154" s="114"/>
       <c r="D154" s="227"/>
-      <c r="E154" s="242"/>
-      <c r="F154" s="243"/>
+      <c r="E154" s="306"/>
+      <c r="F154" s="307"/>
       <c r="G154" s="228"/>
       <c r="H154" s="228"/>
       <c r="I154" s="228"/>
@@ -11384,8 +11387,8 @@
       </c>
       <c r="C155" s="114"/>
       <c r="D155" s="227"/>
-      <c r="E155" s="242"/>
-      <c r="F155" s="243"/>
+      <c r="E155" s="306"/>
+      <c r="F155" s="307"/>
       <c r="G155" s="228"/>
       <c r="H155" s="228"/>
       <c r="I155" s="228"/>
@@ -11408,8 +11411,8 @@
       </c>
       <c r="C156" s="114"/>
       <c r="D156" s="227"/>
-      <c r="E156" s="242"/>
-      <c r="F156" s="243"/>
+      <c r="E156" s="306"/>
+      <c r="F156" s="307"/>
       <c r="G156" s="228"/>
       <c r="H156" s="228"/>
       <c r="I156" s="228"/>
@@ -11432,8 +11435,8 @@
       </c>
       <c r="C157" s="114"/>
       <c r="D157" s="227"/>
-      <c r="E157" s="242"/>
-      <c r="F157" s="243"/>
+      <c r="E157" s="306"/>
+      <c r="F157" s="307"/>
       <c r="G157" s="228"/>
       <c r="H157" s="228"/>
       <c r="I157" s="228"/>
@@ -11456,8 +11459,8 @@
       </c>
       <c r="C158" s="114"/>
       <c r="D158" s="227"/>
-      <c r="E158" s="242"/>
-      <c r="F158" s="243"/>
+      <c r="E158" s="306"/>
+      <c r="F158" s="307"/>
       <c r="G158" s="228"/>
       <c r="H158" s="228"/>
       <c r="I158" s="228"/>
@@ -11480,8 +11483,8 @@
       </c>
       <c r="C159" s="114"/>
       <c r="D159" s="227"/>
-      <c r="E159" s="242"/>
-      <c r="F159" s="243"/>
+      <c r="E159" s="306"/>
+      <c r="F159" s="307"/>
       <c r="G159" s="228"/>
       <c r="H159" s="228"/>
       <c r="I159" s="228"/>
@@ -11504,8 +11507,8 @@
       </c>
       <c r="C160" s="114"/>
       <c r="D160" s="227"/>
-      <c r="E160" s="242"/>
-      <c r="F160" s="243"/>
+      <c r="E160" s="306"/>
+      <c r="F160" s="307"/>
       <c r="G160" s="228"/>
       <c r="H160" s="228"/>
       <c r="I160" s="228"/>
@@ -11528,8 +11531,8 @@
       </c>
       <c r="C161" s="114"/>
       <c r="D161" s="227"/>
-      <c r="E161" s="242"/>
-      <c r="F161" s="243"/>
+      <c r="E161" s="306"/>
+      <c r="F161" s="307"/>
       <c r="G161" s="228"/>
       <c r="H161" s="228"/>
       <c r="I161" s="228"/>
@@ -11552,8 +11555,8 @@
       </c>
       <c r="C162" s="114"/>
       <c r="D162" s="227"/>
-      <c r="E162" s="242"/>
-      <c r="F162" s="243"/>
+      <c r="E162" s="306"/>
+      <c r="F162" s="307"/>
       <c r="G162" s="228"/>
       <c r="H162" s="228"/>
       <c r="I162" s="228"/>
@@ -11576,8 +11579,8 @@
       </c>
       <c r="C163" s="114"/>
       <c r="D163" s="227"/>
-      <c r="E163" s="242"/>
-      <c r="F163" s="243"/>
+      <c r="E163" s="306"/>
+      <c r="F163" s="307"/>
       <c r="G163" s="228"/>
       <c r="H163" s="228"/>
       <c r="I163" s="228"/>
@@ -11600,8 +11603,8 @@
       </c>
       <c r="C164" s="114"/>
       <c r="D164" s="227"/>
-      <c r="E164" s="242"/>
-      <c r="F164" s="243"/>
+      <c r="E164" s="306"/>
+      <c r="F164" s="307"/>
       <c r="G164" s="228"/>
       <c r="H164" s="228"/>
       <c r="I164" s="228"/>
@@ -11624,8 +11627,8 @@
       </c>
       <c r="C165" s="114"/>
       <c r="D165" s="227"/>
-      <c r="E165" s="242"/>
-      <c r="F165" s="243"/>
+      <c r="E165" s="306"/>
+      <c r="F165" s="307"/>
       <c r="G165" s="228"/>
       <c r="H165" s="228"/>
       <c r="I165" s="228"/>
@@ -11648,8 +11651,8 @@
       </c>
       <c r="C166" s="114"/>
       <c r="D166" s="227"/>
-      <c r="E166" s="242"/>
-      <c r="F166" s="243"/>
+      <c r="E166" s="306"/>
+      <c r="F166" s="307"/>
       <c r="G166" s="228"/>
       <c r="H166" s="228"/>
       <c r="I166" s="228"/>
@@ -11672,8 +11675,8 @@
       </c>
       <c r="C167" s="114"/>
       <c r="D167" s="227"/>
-      <c r="E167" s="242"/>
-      <c r="F167" s="243"/>
+      <c r="E167" s="306"/>
+      <c r="F167" s="307"/>
       <c r="G167" s="228"/>
       <c r="H167" s="228"/>
       <c r="I167" s="228"/>
@@ -11696,8 +11699,8 @@
       </c>
       <c r="C168" s="114"/>
       <c r="D168" s="227"/>
-      <c r="E168" s="242"/>
-      <c r="F168" s="243"/>
+      <c r="E168" s="306"/>
+      <c r="F168" s="307"/>
       <c r="G168" s="228"/>
       <c r="H168" s="228"/>
       <c r="I168" s="228"/>
@@ -11720,8 +11723,8 @@
       </c>
       <c r="C169" s="114"/>
       <c r="D169" s="227"/>
-      <c r="E169" s="242"/>
-      <c r="F169" s="243"/>
+      <c r="E169" s="306"/>
+      <c r="F169" s="307"/>
       <c r="G169" s="228"/>
       <c r="H169" s="228"/>
       <c r="I169" s="228"/>
@@ -11744,8 +11747,8 @@
       </c>
       <c r="C170" s="114"/>
       <c r="D170" s="227"/>
-      <c r="E170" s="242"/>
-      <c r="F170" s="243"/>
+      <c r="E170" s="306"/>
+      <c r="F170" s="307"/>
       <c r="G170" s="228"/>
       <c r="H170" s="228"/>
       <c r="I170" s="228"/>
@@ -11768,8 +11771,8 @@
       </c>
       <c r="C171" s="114"/>
       <c r="D171" s="227"/>
-      <c r="E171" s="242"/>
-      <c r="F171" s="243"/>
+      <c r="E171" s="306"/>
+      <c r="F171" s="307"/>
       <c r="G171" s="228"/>
       <c r="H171" s="228"/>
       <c r="I171" s="228"/>
@@ -11792,8 +11795,8 @@
         <f>SUM(D72:D171)</f>
         <v>0</v>
       </c>
-      <c r="E172" s="268"/>
-      <c r="F172" s="269"/>
+      <c r="E172" s="304"/>
+      <c r="F172" s="305"/>
       <c r="G172" s="116">
         <f>SUMPRODUCT($D$72:$D$171,G72:G171)</f>
         <v>0</v>
@@ -11831,21 +11834,21 @@
       <c r="B174" s="8" t="s">
         <v>852</v>
       </c>
-      <c r="D174" s="305" t="s">
+      <c r="D174" s="274" t="s">
         <v>854</v>
       </c>
-      <c r="E174" s="305"/>
-      <c r="F174" s="305"/>
+      <c r="E174" s="274"/>
+      <c r="F174" s="274"/>
       <c r="G174" s="240">
         <f t="array" ref="G174">IFERROR(SUMPRODUCT((C72:C171="")*(D72:D171)*(J72:J171))/I66,0)</f>
         <v>0</v>
       </c>
-      <c r="H174" s="305" t="s">
+      <c r="H174" s="274" t="s">
         <v>855</v>
       </c>
-      <c r="I174" s="305"/>
-      <c r="J174" s="305"/>
-      <c r="K174" s="305"/>
+      <c r="I174" s="274"/>
+      <c r="J174" s="274"/>
+      <c r="K174" s="274"/>
       <c r="L174" s="240">
         <f t="array" ref="L174">IFERROR(SUMPRODUCT((C72:C171="C")*(D72:D171)*(J72:J171))/I66,0)</f>
         <v>0</v>
@@ -11859,17 +11862,17 @@
       <c r="E176" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="F176" s="325" t="s">
+      <c r="F176" s="246" t="s">
         <v>868</v>
       </c>
-      <c r="G176" s="325"/>
-      <c r="H176" s="325"/>
+      <c r="G176" s="246"/>
+      <c r="H176" s="246"/>
       <c r="I176" s="145"/>
       <c r="J176" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="K176" s="310"/>
-      <c r="L176" s="310"/>
+      <c r="K176" s="258"/>
+      <c r="L176" s="258"/>
       <c r="M176" s="174"/>
       <c r="N176" s="174"/>
       <c r="O176" s="174"/>
@@ -11899,11 +11902,11 @@
       <c r="E178" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="F178" s="328" t="s">
+      <c r="F178" s="249" t="s">
         <v>875</v>
       </c>
-      <c r="G178" s="329"/>
-      <c r="H178" s="329"/>
+      <c r="G178" s="250"/>
+      <c r="H178" s="250"/>
       <c r="I178" s="150">
         <v>2397.4499999999998</v>
       </c>
@@ -11950,18 +11953,20 @@
     </row>
     <row r="181" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="238"/>
-      <c r="B181" s="320" t="str">
+      <c r="B181" s="281" t="str">
         <f>IF($F$30&lt;&gt;"sim","Valor proposto do terreno:","Valor proposto do terreno para o módulo:")</f>
         <v>Valor proposto do terreno:</v>
       </c>
-      <c r="C181" s="320"/>
-      <c r="D181" s="320"/>
+      <c r="C181" s="281"/>
+      <c r="D181" s="281"/>
       <c r="E181" s="222" t="s">
         <v>869</v>
       </c>
-      <c r="F181" s="326"/>
-      <c r="G181" s="327"/>
-      <c r="H181" s="327"/>
+      <c r="F181" s="247" t="s">
+        <v>901</v>
+      </c>
+      <c r="G181" s="248"/>
+      <c r="H181" s="248"/>
       <c r="I181" s="145" t="s">
         <v>833</v>
       </c>
@@ -11986,8 +11991,8 @@
       <c r="J183" s="4" t="s">
         <v>834</v>
       </c>
-      <c r="K183" s="319"/>
-      <c r="L183" s="319"/>
+      <c r="K183" s="280"/>
+      <c r="L183" s="280"/>
       <c r="M183" s="145"/>
       <c r="N183" s="145"/>
       <c r="O183" s="145"/>
@@ -12015,7 +12020,7 @@
       <c r="O185" s="145"/>
     </row>
     <row r="186" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A186" s="244"/>
+      <c r="A186" s="329"/>
       <c r="B186" s="8" t="s">
         <v>39</v>
       </c>
@@ -12036,18 +12041,18 @@
       <c r="R186" s="127"/>
     </row>
     <row r="187" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A187" s="244"/>
+      <c r="A187" s="329"/>
       <c r="B187" s="145"/>
       <c r="C187" s="145"/>
       <c r="D187" s="145"/>
       <c r="E187" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="F187" s="251">
+      <c r="F187" s="300">
         <f>I178*K172</f>
         <v>0</v>
       </c>
-      <c r="G187" s="251"/>
+      <c r="G187" s="300"/>
       <c r="H187" s="218"/>
       <c r="I187" s="4" t="s">
         <v>41</v>
@@ -12059,12 +12064,12 @@
       <c r="L187" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="M187" s="251">
+      <c r="M187" s="300">
         <f>ROUND(F187*(1+J187),2)</f>
         <v>0</v>
       </c>
-      <c r="N187" s="251"/>
-      <c r="O187" s="251"/>
+      <c r="N187" s="300"/>
+      <c r="O187" s="300"/>
       <c r="P187" s="177"/>
       <c r="Q187">
         <f>IF(OR(programa=$A$5,programa=$A$6),0,Orç_analítico_Hab!M430)</f>
@@ -12076,7 +12081,7 @@
       </c>
     </row>
     <row r="188" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A188" s="244"/>
+      <c r="A188" s="329"/>
       <c r="B188" s="145"/>
       <c r="C188" s="145"/>
       <c r="D188" s="145"/>
@@ -12104,7 +12109,7 @@
       <c r="P188" s="154"/>
     </row>
     <row r="189" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A189" s="244"/>
+      <c r="A189" s="329"/>
       <c r="B189" s="8" t="s">
         <v>43</v>
       </c>
@@ -12127,17 +12132,17 @@
       <c r="P189" s="145"/>
     </row>
     <row r="190" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A190" s="244"/>
+      <c r="A190" s="329"/>
       <c r="B190" s="145"/>
       <c r="C190" s="145"/>
       <c r="D190" s="145"/>
       <c r="E190" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="F190" s="251">
-        <v>0</v>
-      </c>
-      <c r="G190" s="251"/>
+      <c r="F190" s="300">
+        <v>0</v>
+      </c>
+      <c r="G190" s="300"/>
       <c r="H190" s="218"/>
       <c r="I190" s="4" t="s">
         <v>41</v>
@@ -12149,16 +12154,16 @@
       <c r="L190" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="M190" s="251">
+      <c r="M190" s="300">
         <f>F190*(1+J190)</f>
         <v>0</v>
       </c>
-      <c r="N190" s="251"/>
-      <c r="O190" s="251"/>
+      <c r="N190" s="300"/>
+      <c r="O190" s="300"/>
       <c r="P190" s="177"/>
     </row>
     <row r="191" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A191" s="244"/>
+      <c r="A191" s="329"/>
       <c r="B191" s="145"/>
       <c r="C191" s="145"/>
       <c r="D191" s="145"/>
@@ -12181,7 +12186,7 @@
       <c r="P191" s="154"/>
     </row>
     <row r="192" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A192" s="244"/>
+      <c r="A192" s="329"/>
       <c r="B192" s="8" t="s">
         <v>44</v>
       </c>
@@ -12201,17 +12206,17 @@
       <c r="P192" s="145"/>
     </row>
     <row r="193" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A193" s="244"/>
+      <c r="A193" s="329"/>
       <c r="B193" s="145"/>
       <c r="C193" s="145"/>
       <c r="D193" s="180"/>
       <c r="E193" s="181" t="s">
         <v>40</v>
       </c>
-      <c r="F193" s="251">
-        <v>0</v>
-      </c>
-      <c r="G193" s="251"/>
+      <c r="F193" s="300">
+        <v>0</v>
+      </c>
+      <c r="G193" s="300"/>
       <c r="H193" s="218"/>
       <c r="I193" s="181" t="s">
         <v>41</v>
@@ -12224,16 +12229,16 @@
       <c r="L193" s="181" t="s">
         <v>42</v>
       </c>
-      <c r="M193" s="252">
+      <c r="M193" s="326">
         <f>F193*(1+J193)</f>
         <v>0</v>
       </c>
-      <c r="N193" s="252"/>
-      <c r="O193" s="252"/>
+      <c r="N193" s="326"/>
+      <c r="O193" s="326"/>
       <c r="P193" s="177"/>
     </row>
     <row r="194" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A194" s="244"/>
+      <c r="A194" s="329"/>
       <c r="B194" s="145"/>
       <c r="C194" s="145"/>
       <c r="D194" s="180"/>
@@ -12256,7 +12261,7 @@
       <c r="P194" s="154"/>
     </row>
     <row r="195" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A195" s="244"/>
+      <c r="A195" s="329"/>
       <c r="B195" s="145"/>
       <c r="C195" s="145"/>
       <c r="D195" s="145"/>
@@ -12270,16 +12275,16 @@
       <c r="L195" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="M195" s="254">
+      <c r="M195" s="327">
         <f>IF(OR(N189&lt;"0",N189="não"),SUM(M187,M193),IF(programa=$A$6,M190,SUM(M187,M193,M190)))</f>
         <v>0</v>
       </c>
-      <c r="N195" s="254"/>
-      <c r="O195" s="255"/>
+      <c r="N195" s="327"/>
+      <c r="O195" s="328"/>
       <c r="P195" s="177"/>
     </row>
     <row r="196" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A196" s="244"/>
+      <c r="A196" s="329"/>
       <c r="B196" s="145"/>
       <c r="C196" s="145"/>
       <c r="D196" s="145"/>
@@ -12308,7 +12313,7 @@
       <c r="P196" s="154"/>
     </row>
     <row r="197" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A197" s="244"/>
+      <c r="A197" s="329"/>
       <c r="B197" s="8" t="s">
         <v>50</v>
       </c>
@@ -12333,7 +12338,7 @@
       <c r="S197" s="211"/>
     </row>
     <row r="198" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A198" s="244"/>
+      <c r="A198" s="329"/>
       <c r="B198" s="145"/>
       <c r="C198" s="145"/>
       <c r="D198" s="145"/>
@@ -12341,12 +12346,12 @@
       <c r="F198" s="4" t="s">
         <v>696</v>
       </c>
-      <c r="G198" s="253" t="e">
+      <c r="G198" s="318" t="e">
         <f>0.02*$O$172</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H198" s="253"/>
-      <c r="I198" s="253"/>
+      <c r="H198" s="318"/>
+      <c r="I198" s="318"/>
       <c r="J198" s="1" t="s">
         <v>705</v>
       </c>
@@ -12356,15 +12361,15 @@
       <c r="N198" s="145"/>
       <c r="O198" s="145"/>
       <c r="P198" s="145"/>
-      <c r="Q198" s="306" t="e">
+      <c r="Q198" s="254" t="e">
         <f>IF(G198&gt;O172*0.02,"(excedeu limite aceitável)","(ok)")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="R198" s="307"/>
-      <c r="S198" s="308"/>
+      <c r="R198" s="255"/>
+      <c r="S198" s="256"/>
     </row>
     <row r="199" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A199" s="244"/>
+      <c r="A199" s="329"/>
       <c r="B199" s="145"/>
       <c r="C199" s="145"/>
       <c r="D199" s="145"/>
@@ -12372,12 +12377,12 @@
       <c r="F199" s="4" t="s">
         <v>699</v>
       </c>
-      <c r="G199" s="253">
+      <c r="G199" s="318">
         <f>0.05*M195</f>
         <v>0</v>
       </c>
-      <c r="H199" s="253"/>
-      <c r="I199" s="253"/>
+      <c r="H199" s="318"/>
+      <c r="I199" s="318"/>
       <c r="J199" s="1" t="s">
         <v>706</v>
       </c>
@@ -12387,15 +12392,15 @@
       <c r="N199" s="145"/>
       <c r="O199" s="145"/>
       <c r="P199" s="145"/>
-      <c r="Q199" s="306" t="str">
+      <c r="Q199" s="254" t="str">
         <f>IF(OR(G199&lt;M195*0.005,G199&gt;M195*0.05),"(fora do intervalo aceitável)","(ok)")</f>
         <v>(ok)</v>
       </c>
-      <c r="R199" s="307"/>
-      <c r="S199" s="308"/>
+      <c r="R199" s="255"/>
+      <c r="S199" s="256"/>
     </row>
     <row r="200" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A200" s="244"/>
+      <c r="A200" s="329"/>
       <c r="B200" s="145"/>
       <c r="C200" s="145"/>
       <c r="D200" s="145"/>
@@ -12403,12 +12408,12 @@
       <c r="F200" s="4" t="s">
         <v>704</v>
       </c>
-      <c r="G200" s="253">
+      <c r="G200" s="318">
         <f>0.005*M195</f>
         <v>0</v>
       </c>
-      <c r="H200" s="253"/>
-      <c r="I200" s="253"/>
+      <c r="H200" s="318"/>
+      <c r="I200" s="318"/>
       <c r="J200" s="1" t="s">
         <v>707</v>
       </c>
@@ -12418,15 +12423,15 @@
       <c r="N200" s="145"/>
       <c r="O200" s="145"/>
       <c r="P200" s="145"/>
-      <c r="Q200" s="306" t="str">
+      <c r="Q200" s="254" t="str">
         <f>IF(G200&gt;M195*0.005,"(excedeu limite aceitável)","(ok)")</f>
         <v>(ok)</v>
       </c>
-      <c r="R200" s="307"/>
-      <c r="S200" s="308"/>
+      <c r="R200" s="255"/>
+      <c r="S200" s="256"/>
     </row>
     <row r="201" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A201" s="244"/>
+      <c r="A201" s="329"/>
       <c r="B201" s="145"/>
       <c r="C201" s="145"/>
       <c r="D201" s="145"/>
@@ -12434,12 +12439,12 @@
       <c r="F201" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="G201" s="253" t="e">
+      <c r="G201" s="318" t="e">
         <f>0.08*$O$172</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H201" s="253"/>
-      <c r="I201" s="253"/>
+      <c r="H201" s="318"/>
+      <c r="I201" s="318"/>
       <c r="J201" s="6" t="s">
         <v>697</v>
       </c>
@@ -12449,15 +12454,15 @@
       <c r="N201" s="145"/>
       <c r="O201" s="145"/>
       <c r="P201" s="145"/>
-      <c r="Q201" s="309" t="e">
+      <c r="Q201" s="257" t="e">
         <f>IF(OR(G201&lt;O172*0.04,G201&gt;O172*0.08),"(fora do intervalo aceitável)","(ok)")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="R201" s="309"/>
-      <c r="S201" s="309"/>
+      <c r="R201" s="257"/>
+      <c r="S201" s="257"/>
     </row>
     <row r="202" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A202" s="244"/>
+      <c r="A202" s="329"/>
       <c r="B202" s="145"/>
       <c r="C202" s="145"/>
       <c r="D202" s="145"/>
@@ -12465,11 +12470,11 @@
       <c r="F202" s="4" t="s">
         <v>819</v>
       </c>
-      <c r="G202" s="253">
+      <c r="G202" s="318">
         <v>50</v>
       </c>
-      <c r="H202" s="253"/>
-      <c r="I202" s="253"/>
+      <c r="H202" s="318"/>
+      <c r="I202" s="318"/>
       <c r="J202" s="1" t="b">
         <f>IF(OR(programa=$A$7,programa=$A$8),"(1,5% do valor de aquisiçãos das UH + 0,5% se implantado na forma de condominio)")</f>
         <v>0</v>
@@ -12482,7 +12487,7 @@
       <c r="P202" s="145"/>
     </row>
     <row r="203" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A203" s="244"/>
+      <c r="A203" s="329"/>
       <c r="B203" s="145"/>
       <c r="C203" s="145"/>
       <c r="D203" s="145"/>
@@ -12490,11 +12495,11 @@
       <c r="F203" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="G203" s="253">
+      <c r="G203" s="318">
         <v>60</v>
       </c>
-      <c r="H203" s="253"/>
-      <c r="I203" s="253"/>
+      <c r="H203" s="318"/>
+      <c r="I203" s="318"/>
       <c r="J203" s="145"/>
       <c r="K203" s="145"/>
       <c r="L203" s="145"/>
@@ -12504,7 +12509,7 @@
       <c r="P203" s="145"/>
     </row>
     <row r="204" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A204" s="244"/>
+      <c r="A204" s="329"/>
       <c r="B204" s="145"/>
       <c r="C204" s="145"/>
       <c r="D204" s="145"/>
@@ -12518,16 +12523,16 @@
       <c r="L204" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="M204" s="251" t="e">
+      <c r="M204" s="300" t="e">
         <f>IF(A12=1,SUM(G198,G200:I203),SUM(G198:I201))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="N204" s="251"/>
-      <c r="O204" s="251"/>
+      <c r="N204" s="300"/>
+      <c r="O204" s="300"/>
       <c r="P204" s="177"/>
     </row>
     <row r="205" spans="1:19" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A205" s="244"/>
+      <c r="A205" s="329"/>
       <c r="B205" s="145"/>
       <c r="C205" s="145"/>
       <c r="D205" s="145"/>
@@ -12545,7 +12550,7 @@
       <c r="P205" s="145"/>
     </row>
     <row r="206" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A206" s="244"/>
+      <c r="A206" s="329"/>
       <c r="B206" s="145"/>
       <c r="C206" s="145"/>
       <c r="D206" s="145"/>
@@ -12559,16 +12564,16 @@
       <c r="L206" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="M206" s="254" t="e">
+      <c r="M206" s="327" t="e">
         <f>M195+M204+F181</f>
         <v>#VALUE!</v>
       </c>
-      <c r="N206" s="254"/>
-      <c r="O206" s="255"/>
+      <c r="N206" s="327"/>
+      <c r="O206" s="328"/>
       <c r="P206" s="177"/>
     </row>
     <row r="207" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A207" s="244"/>
+      <c r="A207" s="329"/>
       <c r="B207" s="145"/>
       <c r="C207" s="145"/>
       <c r="D207" s="145"/>
@@ -12604,11 +12609,11 @@
       <c r="D208" s="145"/>
       <c r="E208" s="145"/>
       <c r="F208" s="145"/>
-      <c r="G208" s="291" t="s">
+      <c r="G208" s="259" t="s">
         <v>54</v>
       </c>
-      <c r="H208" s="291"/>
-      <c r="I208" s="291"/>
+      <c r="H208" s="259"/>
+      <c r="I208" s="259"/>
       <c r="J208" s="145"/>
       <c r="K208" s="118" t="s">
         <v>701</v>
@@ -12621,54 +12626,54 @@
     </row>
     <row r="209" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A209" s="237"/>
-      <c r="B209" s="246"/>
-      <c r="C209" s="246"/>
-      <c r="D209" s="246"/>
-      <c r="E209" s="246"/>
+      <c r="B209" s="260"/>
+      <c r="C209" s="260"/>
+      <c r="D209" s="260"/>
+      <c r="E209" s="260"/>
       <c r="F209" s="145"/>
-      <c r="G209" s="263"/>
-      <c r="H209" s="263"/>
-      <c r="I209" s="263"/>
+      <c r="G209" s="299"/>
+      <c r="H209" s="299"/>
+      <c r="I209" s="299"/>
       <c r="J209" s="145"/>
-      <c r="K209" s="246"/>
-      <c r="L209" s="246"/>
-      <c r="M209" s="246"/>
-      <c r="N209" s="246"/>
-      <c r="O209" s="246"/>
+      <c r="K209" s="260"/>
+      <c r="L209" s="260"/>
+      <c r="M209" s="260"/>
+      <c r="N209" s="260"/>
+      <c r="O209" s="260"/>
       <c r="P209" s="145"/>
     </row>
     <row r="210" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B210" s="246"/>
-      <c r="C210" s="246"/>
-      <c r="D210" s="246"/>
-      <c r="E210" s="246"/>
+      <c r="B210" s="260"/>
+      <c r="C210" s="260"/>
+      <c r="D210" s="260"/>
+      <c r="E210" s="260"/>
       <c r="F210" s="145"/>
-      <c r="G210" s="263"/>
-      <c r="H210" s="263"/>
-      <c r="I210" s="263"/>
+      <c r="G210" s="299"/>
+      <c r="H210" s="299"/>
+      <c r="I210" s="299"/>
       <c r="J210" s="145"/>
-      <c r="K210" s="246"/>
-      <c r="L210" s="246"/>
-      <c r="M210" s="246"/>
-      <c r="N210" s="246"/>
-      <c r="O210" s="246"/>
+      <c r="K210" s="260"/>
+      <c r="L210" s="260"/>
+      <c r="M210" s="260"/>
+      <c r="N210" s="260"/>
+      <c r="O210" s="260"/>
       <c r="P210" s="145"/>
     </row>
     <row r="211" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B211" s="246"/>
-      <c r="C211" s="246"/>
-      <c r="D211" s="246"/>
-      <c r="E211" s="246"/>
+      <c r="B211" s="260"/>
+      <c r="C211" s="260"/>
+      <c r="D211" s="260"/>
+      <c r="E211" s="260"/>
       <c r="F211" s="145"/>
-      <c r="G211" s="263"/>
-      <c r="H211" s="263"/>
-      <c r="I211" s="263"/>
+      <c r="G211" s="299"/>
+      <c r="H211" s="299"/>
+      <c r="I211" s="299"/>
       <c r="J211" s="145"/>
-      <c r="K211" s="246"/>
-      <c r="L211" s="246"/>
-      <c r="M211" s="246"/>
-      <c r="N211" s="246"/>
-      <c r="O211" s="246"/>
+      <c r="K211" s="260"/>
+      <c r="L211" s="260"/>
+      <c r="M211" s="260"/>
+      <c r="N211" s="260"/>
+      <c r="O211" s="260"/>
       <c r="P211" s="145"/>
     </row>
     <row r="212" spans="1:16" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3">
@@ -12696,11 +12701,11 @@
       <c r="D213" s="145"/>
       <c r="E213" s="145"/>
       <c r="F213" s="145"/>
-      <c r="G213" s="291" t="s">
+      <c r="G213" s="259" t="s">
         <v>54</v>
       </c>
-      <c r="H213" s="291"/>
-      <c r="I213" s="291"/>
+      <c r="H213" s="259"/>
+      <c r="I213" s="259"/>
       <c r="J213" s="145"/>
       <c r="K213" s="145"/>
       <c r="L213" s="145"/>
@@ -12710,14 +12715,14 @@
       <c r="P213" s="145"/>
     </row>
     <row r="214" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B214" s="246"/>
-      <c r="C214" s="246"/>
-      <c r="D214" s="246"/>
-      <c r="E214" s="246"/>
+      <c r="B214" s="260"/>
+      <c r="C214" s="260"/>
+      <c r="D214" s="260"/>
+      <c r="E214" s="260"/>
       <c r="F214" s="145"/>
-      <c r="G214" s="263"/>
-      <c r="H214" s="263"/>
-      <c r="I214" s="263"/>
+      <c r="G214" s="299"/>
+      <c r="H214" s="299"/>
+      <c r="I214" s="299"/>
       <c r="J214" s="145"/>
       <c r="K214" s="145"/>
       <c r="L214" s="145"/>
@@ -12727,14 +12732,14 @@
       <c r="P214" s="145"/>
     </row>
     <row r="215" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B215" s="246"/>
-      <c r="C215" s="246"/>
-      <c r="D215" s="246"/>
-      <c r="E215" s="246"/>
+      <c r="B215" s="260"/>
+      <c r="C215" s="260"/>
+      <c r="D215" s="260"/>
+      <c r="E215" s="260"/>
       <c r="F215" s="145"/>
-      <c r="G215" s="263"/>
-      <c r="H215" s="263"/>
-      <c r="I215" s="263"/>
+      <c r="G215" s="299"/>
+      <c r="H215" s="299"/>
+      <c r="I215" s="299"/>
       <c r="J215" s="145"/>
       <c r="K215" s="145"/>
       <c r="L215" s="145"/>
@@ -12744,25 +12749,25 @@
       <c r="P215" s="145"/>
     </row>
     <row r="216" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B216" s="246"/>
-      <c r="C216" s="246"/>
-      <c r="D216" s="246"/>
-      <c r="E216" s="246"/>
+      <c r="B216" s="260"/>
+      <c r="C216" s="260"/>
+      <c r="D216" s="260"/>
+      <c r="E216" s="260"/>
       <c r="F216" s="145"/>
-      <c r="G216" s="263"/>
-      <c r="H216" s="263"/>
-      <c r="I216" s="263"/>
+      <c r="G216" s="299"/>
+      <c r="H216" s="299"/>
+      <c r="I216" s="299"/>
       <c r="J216" s="161"/>
       <c r="K216" s="162"/>
       <c r="L216" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="M216" s="247" t="e">
+      <c r="M216" s="322" t="e">
         <f>O172</f>
         <v>#VALUE!</v>
       </c>
-      <c r="N216" s="247"/>
-      <c r="O216" s="248"/>
+      <c r="N216" s="322"/>
+      <c r="O216" s="323"/>
       <c r="P216" s="177"/>
     </row>
     <row r="217" spans="1:16" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3">
@@ -12802,39 +12807,39 @@
       <c r="P218" s="145"/>
     </row>
     <row r="219" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B219" s="249" t="s">
+      <c r="B219" s="324" t="s">
         <v>896</v>
       </c>
-      <c r="C219" s="250"/>
-      <c r="D219" s="250"/>
-      <c r="E219" s="250"/>
-      <c r="F219" s="250"/>
-      <c r="G219" s="250"/>
-      <c r="H219" s="250"/>
-      <c r="I219" s="250"/>
-      <c r="J219" s="250"/>
-      <c r="K219" s="250"/>
-      <c r="L219" s="250"/>
-      <c r="M219" s="250"/>
-      <c r="N219" s="250"/>
-      <c r="O219" s="250"/>
+      <c r="C219" s="325"/>
+      <c r="D219" s="325"/>
+      <c r="E219" s="325"/>
+      <c r="F219" s="325"/>
+      <c r="G219" s="325"/>
+      <c r="H219" s="325"/>
+      <c r="I219" s="325"/>
+      <c r="J219" s="325"/>
+      <c r="K219" s="325"/>
+      <c r="L219" s="325"/>
+      <c r="M219" s="325"/>
+      <c r="N219" s="325"/>
+      <c r="O219" s="325"/>
       <c r="P219" s="171"/>
     </row>
     <row r="220" spans="1:16" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B220" s="249"/>
-      <c r="C220" s="250"/>
-      <c r="D220" s="250"/>
-      <c r="E220" s="250"/>
-      <c r="F220" s="250"/>
-      <c r="G220" s="250"/>
-      <c r="H220" s="250"/>
-      <c r="I220" s="250"/>
-      <c r="J220" s="250"/>
-      <c r="K220" s="250"/>
-      <c r="L220" s="250"/>
-      <c r="M220" s="250"/>
-      <c r="N220" s="250"/>
-      <c r="O220" s="250"/>
+      <c r="B220" s="324"/>
+      <c r="C220" s="325"/>
+      <c r="D220" s="325"/>
+      <c r="E220" s="325"/>
+      <c r="F220" s="325"/>
+      <c r="G220" s="325"/>
+      <c r="H220" s="325"/>
+      <c r="I220" s="325"/>
+      <c r="J220" s="325"/>
+      <c r="K220" s="325"/>
+      <c r="L220" s="325"/>
+      <c r="M220" s="325"/>
+      <c r="N220" s="325"/>
+      <c r="O220" s="325"/>
       <c r="P220" s="171"/>
     </row>
     <row r="221" spans="1:16" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -12877,14 +12882,14 @@
       <c r="B223" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C223" s="311" t="str">
+      <c r="C223" s="263" t="str">
         <f>B16</f>
         <v>{PROPONENTE}</v>
       </c>
-      <c r="D223" s="312"/>
-      <c r="E223" s="312"/>
-      <c r="F223" s="312"/>
-      <c r="G223" s="312"/>
+      <c r="D223" s="264"/>
+      <c r="E223" s="264"/>
+      <c r="F223" s="264"/>
+      <c r="G223" s="264"/>
       <c r="H223" s="235"/>
       <c r="I223" s="145"/>
       <c r="J223" s="145"/>
@@ -12899,14 +12904,14 @@
       <c r="B224" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="C224" s="312" t="str">
+      <c r="C224" s="264" t="str">
         <f>M16</f>
         <v>{DOC. PROPONENTE}</v>
       </c>
-      <c r="D224" s="312"/>
-      <c r="E224" s="312"/>
-      <c r="F224" s="312"/>
-      <c r="G224" s="312"/>
+      <c r="D224" s="264"/>
+      <c r="E224" s="264"/>
+      <c r="F224" s="264"/>
+      <c r="G224" s="264"/>
       <c r="H224" s="236"/>
       <c r="I224" s="145"/>
       <c r="J224" s="145"/>
@@ -12938,13 +12943,13 @@
       <c r="B226" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="C226" s="312" t="s">
+      <c r="C226" s="264" t="s">
         <v>873</v>
       </c>
-      <c r="D226" s="312"/>
-      <c r="E226" s="312"/>
-      <c r="F226" s="312"/>
-      <c r="G226" s="312"/>
+      <c r="D226" s="264"/>
+      <c r="E226" s="264"/>
+      <c r="F226" s="264"/>
+      <c r="G226" s="264"/>
       <c r="H226" s="235"/>
       <c r="I226" s="145"/>
       <c r="J226" s="145"/>
@@ -12959,10 +12964,10 @@
       <c r="B227" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C227" s="304" t="s">
+      <c r="C227" s="284" t="s">
         <v>895</v>
       </c>
-      <c r="D227" s="304"/>
+      <c r="D227" s="284"/>
       <c r="E227" s="145"/>
       <c r="F227" s="145"/>
       <c r="G227" s="145"/>
@@ -12979,15 +12984,157 @@
   </sheetData>
   <sheetProtection insertRows="0"/>
   <mergeCells count="199">
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="F176:H176"/>
-    <mergeCell ref="F181:H181"/>
-    <mergeCell ref="F178:H178"/>
-    <mergeCell ref="N47:O47"/>
-    <mergeCell ref="C69:C71"/>
-    <mergeCell ref="Q198:S198"/>
-    <mergeCell ref="Q199:S199"/>
+    <mergeCell ref="E169:F169"/>
+    <mergeCell ref="E170:F170"/>
+    <mergeCell ref="E171:F171"/>
+    <mergeCell ref="A186:A207"/>
+    <mergeCell ref="A72:A91"/>
+    <mergeCell ref="E163:F163"/>
+    <mergeCell ref="E164:F164"/>
+    <mergeCell ref="E165:F165"/>
+    <mergeCell ref="E166:F166"/>
+    <mergeCell ref="E167:F167"/>
+    <mergeCell ref="E168:F168"/>
+    <mergeCell ref="E157:F157"/>
+    <mergeCell ref="E158:F158"/>
+    <mergeCell ref="E159:F159"/>
+    <mergeCell ref="E160:F160"/>
+    <mergeCell ref="E161:F161"/>
+    <mergeCell ref="E162:F162"/>
+    <mergeCell ref="E151:F151"/>
+    <mergeCell ref="E152:F152"/>
+    <mergeCell ref="E153:F153"/>
+    <mergeCell ref="E154:F154"/>
+    <mergeCell ref="E155:F155"/>
+    <mergeCell ref="E156:F156"/>
+    <mergeCell ref="E145:F145"/>
+    <mergeCell ref="E146:F146"/>
+    <mergeCell ref="E147:F147"/>
+    <mergeCell ref="E148:F148"/>
+    <mergeCell ref="E149:F149"/>
+    <mergeCell ref="E150:F150"/>
+    <mergeCell ref="E139:F139"/>
+    <mergeCell ref="E140:F140"/>
+    <mergeCell ref="E141:F141"/>
+    <mergeCell ref="E142:F142"/>
+    <mergeCell ref="E143:F143"/>
+    <mergeCell ref="E144:F144"/>
+    <mergeCell ref="E134:F134"/>
+    <mergeCell ref="E135:F135"/>
+    <mergeCell ref="E136:F136"/>
+    <mergeCell ref="E137:F137"/>
+    <mergeCell ref="E138:F138"/>
+    <mergeCell ref="E127:F127"/>
+    <mergeCell ref="E128:F128"/>
+    <mergeCell ref="E129:F129"/>
+    <mergeCell ref="E130:F130"/>
+    <mergeCell ref="E131:F131"/>
+    <mergeCell ref="E132:F132"/>
+    <mergeCell ref="E125:F125"/>
+    <mergeCell ref="E126:F126"/>
+    <mergeCell ref="E115:F115"/>
+    <mergeCell ref="E116:F116"/>
+    <mergeCell ref="E117:F117"/>
+    <mergeCell ref="E118:F118"/>
+    <mergeCell ref="E119:F119"/>
+    <mergeCell ref="E120:F120"/>
+    <mergeCell ref="E133:F133"/>
+    <mergeCell ref="G216:I216"/>
+    <mergeCell ref="B214:E214"/>
+    <mergeCell ref="E97:F97"/>
+    <mergeCell ref="E98:F98"/>
+    <mergeCell ref="E99:F99"/>
+    <mergeCell ref="E100:F100"/>
+    <mergeCell ref="E101:F101"/>
+    <mergeCell ref="E102:F102"/>
+    <mergeCell ref="E91:F91"/>
+    <mergeCell ref="E92:F92"/>
+    <mergeCell ref="E93:F93"/>
+    <mergeCell ref="E94:F94"/>
+    <mergeCell ref="E95:F95"/>
+    <mergeCell ref="E96:F96"/>
+    <mergeCell ref="E109:F109"/>
+    <mergeCell ref="E110:F110"/>
+    <mergeCell ref="E111:F111"/>
+    <mergeCell ref="E112:F112"/>
+    <mergeCell ref="E113:F113"/>
+    <mergeCell ref="E114:F114"/>
+    <mergeCell ref="E103:F103"/>
+    <mergeCell ref="E104:F104"/>
+    <mergeCell ref="E105:F105"/>
+    <mergeCell ref="E106:F106"/>
+    <mergeCell ref="J28:L28"/>
+    <mergeCell ref="B10:L10"/>
+    <mergeCell ref="K211:O211"/>
+    <mergeCell ref="M216:O216"/>
+    <mergeCell ref="B219:O220"/>
+    <mergeCell ref="M190:O190"/>
+    <mergeCell ref="M187:O187"/>
+    <mergeCell ref="M193:O193"/>
+    <mergeCell ref="G201:I201"/>
+    <mergeCell ref="K209:O209"/>
+    <mergeCell ref="K210:O210"/>
+    <mergeCell ref="G202:I202"/>
+    <mergeCell ref="M195:O195"/>
+    <mergeCell ref="M204:O204"/>
+    <mergeCell ref="B211:E211"/>
+    <mergeCell ref="B210:E210"/>
+    <mergeCell ref="G209:I209"/>
+    <mergeCell ref="G210:I210"/>
+    <mergeCell ref="G199:I199"/>
+    <mergeCell ref="M206:O206"/>
+    <mergeCell ref="G211:I211"/>
+    <mergeCell ref="G203:I203"/>
+    <mergeCell ref="G200:I200"/>
+    <mergeCell ref="B216:E216"/>
+    <mergeCell ref="E88:F88"/>
+    <mergeCell ref="E87:F87"/>
+    <mergeCell ref="E80:F80"/>
+    <mergeCell ref="E81:F81"/>
+    <mergeCell ref="E74:F74"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="H69:H70"/>
+    <mergeCell ref="G198:I198"/>
+    <mergeCell ref="E82:F82"/>
+    <mergeCell ref="I69:I71"/>
+    <mergeCell ref="E72:F72"/>
+    <mergeCell ref="E73:F73"/>
+    <mergeCell ref="E90:F90"/>
+    <mergeCell ref="F193:G193"/>
+    <mergeCell ref="E76:F76"/>
+    <mergeCell ref="E77:F77"/>
+    <mergeCell ref="E83:F83"/>
+    <mergeCell ref="F190:G190"/>
+    <mergeCell ref="E107:F107"/>
+    <mergeCell ref="E108:F108"/>
+    <mergeCell ref="E121:F121"/>
+    <mergeCell ref="E122:F122"/>
+    <mergeCell ref="E123:F123"/>
+    <mergeCell ref="E124:F124"/>
+    <mergeCell ref="C227:D227"/>
+    <mergeCell ref="D174:F174"/>
+    <mergeCell ref="C226:G226"/>
+    <mergeCell ref="C224:G224"/>
+    <mergeCell ref="M28:O28"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="B41:O43"/>
+    <mergeCell ref="M69:M71"/>
+    <mergeCell ref="O69:O71"/>
+    <mergeCell ref="K47:M47"/>
+    <mergeCell ref="B69:B71"/>
+    <mergeCell ref="N51:O51"/>
+    <mergeCell ref="G208:I208"/>
+    <mergeCell ref="B62:O64"/>
+    <mergeCell ref="G214:I214"/>
+    <mergeCell ref="B215:E215"/>
+    <mergeCell ref="G215:I215"/>
+    <mergeCell ref="F187:G187"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="I66:J66"/>
+    <mergeCell ref="I67:J67"/>
+    <mergeCell ref="B57:E57"/>
+    <mergeCell ref="E172:F172"/>
+    <mergeCell ref="E86:F86"/>
     <mergeCell ref="Q200:S200"/>
     <mergeCell ref="Q201:S201"/>
     <mergeCell ref="K176:L176"/>
@@ -13012,30 +13159,15 @@
     <mergeCell ref="M19:O19"/>
     <mergeCell ref="M10:O10"/>
     <mergeCell ref="B28:I28"/>
-    <mergeCell ref="C227:D227"/>
-    <mergeCell ref="D174:F174"/>
-    <mergeCell ref="C226:G226"/>
-    <mergeCell ref="C224:G224"/>
-    <mergeCell ref="M28:O28"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="B41:O43"/>
-    <mergeCell ref="M69:M71"/>
-    <mergeCell ref="O69:O71"/>
-    <mergeCell ref="K47:M47"/>
-    <mergeCell ref="B69:B71"/>
-    <mergeCell ref="N51:O51"/>
-    <mergeCell ref="G208:I208"/>
-    <mergeCell ref="B62:O64"/>
-    <mergeCell ref="G214:I214"/>
-    <mergeCell ref="B215:E215"/>
-    <mergeCell ref="G215:I215"/>
-    <mergeCell ref="F187:G187"/>
-    <mergeCell ref="F47:G47"/>
-    <mergeCell ref="I66:J66"/>
-    <mergeCell ref="I67:J67"/>
-    <mergeCell ref="B57:E57"/>
-    <mergeCell ref="E172:F172"/>
-    <mergeCell ref="E86:F86"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="F176:H176"/>
+    <mergeCell ref="F181:H181"/>
+    <mergeCell ref="F178:H178"/>
+    <mergeCell ref="N47:O47"/>
+    <mergeCell ref="C69:C71"/>
+    <mergeCell ref="Q198:S198"/>
+    <mergeCell ref="Q199:S199"/>
     <mergeCell ref="D69:D71"/>
     <mergeCell ref="E69:F71"/>
     <mergeCell ref="E75:F75"/>
@@ -13051,133 +13183,6 @@
     <mergeCell ref="E85:F85"/>
     <mergeCell ref="E84:F84"/>
     <mergeCell ref="E4:J4"/>
-    <mergeCell ref="E88:F88"/>
-    <mergeCell ref="E87:F87"/>
-    <mergeCell ref="E80:F80"/>
-    <mergeCell ref="E81:F81"/>
-    <mergeCell ref="E74:F74"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="H69:H70"/>
-    <mergeCell ref="G198:I198"/>
-    <mergeCell ref="E82:F82"/>
-    <mergeCell ref="I69:I71"/>
-    <mergeCell ref="E72:F72"/>
-    <mergeCell ref="E73:F73"/>
-    <mergeCell ref="E90:F90"/>
-    <mergeCell ref="F193:G193"/>
-    <mergeCell ref="E76:F76"/>
-    <mergeCell ref="E77:F77"/>
-    <mergeCell ref="E83:F83"/>
-    <mergeCell ref="F190:G190"/>
-    <mergeCell ref="J28:L28"/>
-    <mergeCell ref="B10:L10"/>
-    <mergeCell ref="K211:O211"/>
-    <mergeCell ref="M216:O216"/>
-    <mergeCell ref="B219:O220"/>
-    <mergeCell ref="M190:O190"/>
-    <mergeCell ref="M187:O187"/>
-    <mergeCell ref="M193:O193"/>
-    <mergeCell ref="G201:I201"/>
-    <mergeCell ref="K209:O209"/>
-    <mergeCell ref="K210:O210"/>
-    <mergeCell ref="G202:I202"/>
-    <mergeCell ref="M195:O195"/>
-    <mergeCell ref="M204:O204"/>
-    <mergeCell ref="B211:E211"/>
-    <mergeCell ref="B210:E210"/>
-    <mergeCell ref="G209:I209"/>
-    <mergeCell ref="G210:I210"/>
-    <mergeCell ref="G199:I199"/>
-    <mergeCell ref="M206:O206"/>
-    <mergeCell ref="G211:I211"/>
-    <mergeCell ref="G203:I203"/>
-    <mergeCell ref="G200:I200"/>
-    <mergeCell ref="B216:E216"/>
-    <mergeCell ref="G216:I216"/>
-    <mergeCell ref="B214:E214"/>
-    <mergeCell ref="E97:F97"/>
-    <mergeCell ref="E98:F98"/>
-    <mergeCell ref="E99:F99"/>
-    <mergeCell ref="E100:F100"/>
-    <mergeCell ref="E101:F101"/>
-    <mergeCell ref="E102:F102"/>
-    <mergeCell ref="E91:F91"/>
-    <mergeCell ref="E92:F92"/>
-    <mergeCell ref="E93:F93"/>
-    <mergeCell ref="E94:F94"/>
-    <mergeCell ref="E95:F95"/>
-    <mergeCell ref="E96:F96"/>
-    <mergeCell ref="E109:F109"/>
-    <mergeCell ref="E110:F110"/>
-    <mergeCell ref="E111:F111"/>
-    <mergeCell ref="E112:F112"/>
-    <mergeCell ref="E113:F113"/>
-    <mergeCell ref="E114:F114"/>
-    <mergeCell ref="E103:F103"/>
-    <mergeCell ref="E104:F104"/>
-    <mergeCell ref="E105:F105"/>
-    <mergeCell ref="E106:F106"/>
-    <mergeCell ref="E107:F107"/>
-    <mergeCell ref="E108:F108"/>
-    <mergeCell ref="E121:F121"/>
-    <mergeCell ref="E122:F122"/>
-    <mergeCell ref="E123:F123"/>
-    <mergeCell ref="E124:F124"/>
-    <mergeCell ref="E125:F125"/>
-    <mergeCell ref="E126:F126"/>
-    <mergeCell ref="E115:F115"/>
-    <mergeCell ref="E116:F116"/>
-    <mergeCell ref="E117:F117"/>
-    <mergeCell ref="E118:F118"/>
-    <mergeCell ref="E119:F119"/>
-    <mergeCell ref="E120:F120"/>
-    <mergeCell ref="E133:F133"/>
-    <mergeCell ref="E134:F134"/>
-    <mergeCell ref="E135:F135"/>
-    <mergeCell ref="E136:F136"/>
-    <mergeCell ref="E137:F137"/>
-    <mergeCell ref="E138:F138"/>
-    <mergeCell ref="E127:F127"/>
-    <mergeCell ref="E128:F128"/>
-    <mergeCell ref="E129:F129"/>
-    <mergeCell ref="E130:F130"/>
-    <mergeCell ref="E131:F131"/>
-    <mergeCell ref="E132:F132"/>
-    <mergeCell ref="E146:F146"/>
-    <mergeCell ref="E147:F147"/>
-    <mergeCell ref="E148:F148"/>
-    <mergeCell ref="E149:F149"/>
-    <mergeCell ref="E150:F150"/>
-    <mergeCell ref="E139:F139"/>
-    <mergeCell ref="E140:F140"/>
-    <mergeCell ref="E141:F141"/>
-    <mergeCell ref="E142:F142"/>
-    <mergeCell ref="E143:F143"/>
-    <mergeCell ref="E144:F144"/>
-    <mergeCell ref="E169:F169"/>
-    <mergeCell ref="E170:F170"/>
-    <mergeCell ref="E171:F171"/>
-    <mergeCell ref="A186:A207"/>
-    <mergeCell ref="A72:A91"/>
-    <mergeCell ref="E163:F163"/>
-    <mergeCell ref="E164:F164"/>
-    <mergeCell ref="E165:F165"/>
-    <mergeCell ref="E166:F166"/>
-    <mergeCell ref="E167:F167"/>
-    <mergeCell ref="E168:F168"/>
-    <mergeCell ref="E157:F157"/>
-    <mergeCell ref="E158:F158"/>
-    <mergeCell ref="E159:F159"/>
-    <mergeCell ref="E160:F160"/>
-    <mergeCell ref="E161:F161"/>
-    <mergeCell ref="E162:F162"/>
-    <mergeCell ref="E151:F151"/>
-    <mergeCell ref="E152:F152"/>
-    <mergeCell ref="E153:F153"/>
-    <mergeCell ref="E154:F154"/>
-    <mergeCell ref="E155:F155"/>
-    <mergeCell ref="E156:F156"/>
-    <mergeCell ref="E145:F145"/>
   </mergeCells>
   <phoneticPr fontId="25" type="noConversion"/>
   <conditionalFormatting sqref="B13">
@@ -13292,11 +13297,11 @@
     <cfRule type="expression" dxfId="76" priority="32">
       <formula>TRIM(F30)&lt;"0"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="75" priority="31">
+    <cfRule type="cellIs" dxfId="75" priority="30" stopIfTrue="1" operator="equal">
+      <formula>"SIM"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="74" priority="31">
       <formula>F30&lt;"0"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="74" priority="30" stopIfTrue="1" operator="equal">
-      <formula>"SIM"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F176">
@@ -13305,11 +13310,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F187:H187">
-    <cfRule type="expression" dxfId="72" priority="65" stopIfTrue="1">
+    <cfRule type="expression" dxfId="72" priority="64" stopIfTrue="1">
+      <formula>programa="Alocação de Recursos em Construção"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="71" priority="65" stopIfTrue="1">
       <formula>INFRA="não"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="71" priority="64" stopIfTrue="1">
-      <formula>programa="Alocação de Recursos em Construção"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F202:I203">
@@ -13602,10 +13607,10 @@
       <c r="E1" s="144" t="s">
         <v>820</v>
       </c>
-      <c r="K1" s="321" t="s">
+      <c r="K1" s="242" t="s">
         <v>857</v>
       </c>
-      <c r="L1" s="322"/>
+      <c r="L1" s="243"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
@@ -13620,10 +13625,10 @@
         <f>FRE!$E$4</f>
         <v>Apoio à Produção de Imóveis - Pessoa Jurídica</v>
       </c>
-      <c r="K2" s="323" t="s">
+      <c r="K2" s="244" t="s">
         <v>858</v>
       </c>
-      <c r="L2" s="324"/>
+      <c r="L2" s="245"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="18" t="s">
@@ -13686,43 +13691,43 @@
       <c r="Q21" s="27"/>
       <c r="R21" s="27"/>
       <c r="S21" s="27"/>
-      <c r="T21" s="331" t="s">
+      <c r="T21" s="335" t="s">
         <v>191</v>
       </c>
-      <c r="U21" s="331" t="s">
+      <c r="U21" s="335" t="s">
         <v>192</v>
       </c>
-      <c r="V21" s="331" t="s">
+      <c r="V21" s="335" t="s">
         <v>193</v>
       </c>
       <c r="W21" s="25"/>
-      <c r="X21" s="331" t="s">
+      <c r="X21" s="335" t="s">
         <v>191</v>
       </c>
-      <c r="Y21" s="331" t="s">
+      <c r="Y21" s="335" t="s">
         <v>192</v>
       </c>
-      <c r="Z21" s="331" t="s">
+      <c r="Z21" s="335" t="s">
         <v>193</v>
       </c>
       <c r="AA21" s="25"/>
-      <c r="AB21" s="331" t="s">
+      <c r="AB21" s="335" t="s">
         <v>191</v>
       </c>
-      <c r="AC21" s="331" t="s">
+      <c r="AC21" s="335" t="s">
         <v>192</v>
       </c>
-      <c r="AD21" s="331" t="s">
+      <c r="AD21" s="335" t="s">
         <v>193</v>
       </c>
       <c r="AE21" s="27"/>
-      <c r="AF21" s="331" t="s">
+      <c r="AF21" s="335" t="s">
         <v>191</v>
       </c>
-      <c r="AG21" s="331" t="s">
+      <c r="AG21" s="335" t="s">
         <v>192</v>
       </c>
-      <c r="AH21" s="331" t="s">
+      <c r="AH21" s="335" t="s">
         <v>193</v>
       </c>
     </row>
@@ -13730,11 +13735,11 @@
       <c r="B22" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="C22" s="259" t="s">
+      <c r="C22" s="316" t="s">
         <v>78</v>
       </c>
-      <c r="D22" s="259"/>
-      <c r="E22" s="259"/>
+      <c r="D22" s="316"/>
+      <c r="E22" s="316"/>
       <c r="I22" s="18" t="str">
         <f>IF(FRE!$A$12=1,"sim",FRE!N189)</f>
         <v>não</v>
@@ -13744,21 +13749,21 @@
       <c r="Q22" s="128"/>
       <c r="R22" s="27"/>
       <c r="S22" s="27"/>
-      <c r="T22" s="331"/>
-      <c r="U22" s="331"/>
-      <c r="V22" s="331"/>
+      <c r="T22" s="335"/>
+      <c r="U22" s="335"/>
+      <c r="V22" s="335"/>
       <c r="W22" s="25"/>
-      <c r="X22" s="331"/>
-      <c r="Y22" s="331"/>
-      <c r="Z22" s="331"/>
+      <c r="X22" s="335"/>
+      <c r="Y22" s="335"/>
+      <c r="Z22" s="335"/>
       <c r="AA22" s="25"/>
-      <c r="AB22" s="331"/>
-      <c r="AC22" s="331"/>
-      <c r="AD22" s="331"/>
+      <c r="AB22" s="335"/>
+      <c r="AC22" s="335"/>
+      <c r="AD22" s="335"/>
       <c r="AE22" s="25"/>
-      <c r="AF22" s="331"/>
-      <c r="AG22" s="331"/>
-      <c r="AH22" s="331"/>
+      <c r="AF22" s="335"/>
+      <c r="AG22" s="335"/>
+      <c r="AH22" s="335"/>
     </row>
     <row r="23" spans="2:37" ht="8.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="O23" s="34"/>
@@ -13766,21 +13771,21 @@
       <c r="Q23" s="27"/>
       <c r="R23" s="27"/>
       <c r="S23" s="27"/>
-      <c r="T23" s="331"/>
-      <c r="U23" s="331"/>
-      <c r="V23" s="331"/>
+      <c r="T23" s="335"/>
+      <c r="U23" s="335"/>
+      <c r="V23" s="335"/>
       <c r="W23" s="26"/>
-      <c r="X23" s="331"/>
-      <c r="Y23" s="331"/>
-      <c r="Z23" s="331"/>
+      <c r="X23" s="335"/>
+      <c r="Y23" s="335"/>
+      <c r="Z23" s="335"/>
       <c r="AA23" s="27"/>
-      <c r="AB23" s="331"/>
-      <c r="AC23" s="331"/>
-      <c r="AD23" s="331"/>
+      <c r="AB23" s="335"/>
+      <c r="AC23" s="335"/>
+      <c r="AD23" s="335"/>
       <c r="AE23" s="25"/>
-      <c r="AF23" s="331"/>
-      <c r="AG23" s="331"/>
-      <c r="AH23" s="331"/>
+      <c r="AF23" s="335"/>
+      <c r="AG23" s="335"/>
+      <c r="AH23" s="335"/>
     </row>
     <row r="24" spans="2:37" s="19" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="187" t="s">
@@ -13806,31 +13811,31 @@
         <v>200</v>
       </c>
       <c r="N24" s="49"/>
-      <c r="O24" s="339" t="str">
+      <c r="O24" s="331" t="str">
         <f>IF(C22="(escolha)","(escolha a tipologia)",C22)</f>
         <v>Habitacional horizontal</v>
       </c>
-      <c r="P24" s="339"/>
-      <c r="Q24" s="339"/>
+      <c r="P24" s="331"/>
+      <c r="Q24" s="331"/>
       <c r="R24" s="30" t="s">
         <v>194</v>
       </c>
       <c r="S24" s="29"/>
-      <c r="T24" s="331"/>
-      <c r="U24" s="331"/>
-      <c r="V24" s="331"/>
+      <c r="T24" s="335"/>
+      <c r="U24" s="335"/>
+      <c r="V24" s="335"/>
       <c r="W24" s="25"/>
-      <c r="X24" s="331"/>
-      <c r="Y24" s="331"/>
-      <c r="Z24" s="331"/>
+      <c r="X24" s="335"/>
+      <c r="Y24" s="335"/>
+      <c r="Z24" s="335"/>
       <c r="AA24" s="25"/>
-      <c r="AB24" s="331"/>
-      <c r="AC24" s="331"/>
-      <c r="AD24" s="331"/>
+      <c r="AB24" s="335"/>
+      <c r="AC24" s="335"/>
+      <c r="AD24" s="335"/>
       <c r="AE24" s="27"/>
-      <c r="AF24" s="331"/>
-      <c r="AG24" s="331"/>
-      <c r="AH24" s="331"/>
+      <c r="AF24" s="335"/>
+      <c r="AG24" s="335"/>
+      <c r="AH24" s="335"/>
       <c r="AI24" s="19" t="s">
         <v>794</v>
       </c>
@@ -19001,28 +19006,28 @@
       <c r="Q87" s="39"/>
       <c r="R87" s="40"/>
       <c r="S87" s="41"/>
-      <c r="T87" s="336" t="s">
+      <c r="T87" s="333" t="s">
         <v>196</v>
       </c>
-      <c r="U87" s="337"/>
+      <c r="U87" s="334"/>
       <c r="V87" s="31"/>
       <c r="W87" s="27"/>
-      <c r="X87" s="336" t="s">
+      <c r="X87" s="333" t="s">
         <v>196</v>
       </c>
-      <c r="Y87" s="337"/>
+      <c r="Y87" s="334"/>
       <c r="Z87" s="31"/>
       <c r="AA87" s="27"/>
-      <c r="AB87" s="336" t="s">
+      <c r="AB87" s="333" t="s">
         <v>196</v>
       </c>
-      <c r="AC87" s="337"/>
+      <c r="AC87" s="334"/>
       <c r="AD87" s="31"/>
       <c r="AE87" s="27"/>
-      <c r="AF87" s="336" t="s">
+      <c r="AF87" s="333" t="s">
         <v>196</v>
       </c>
-      <c r="AG87" s="337"/>
+      <c r="AG87" s="334"/>
       <c r="AH87" s="30"/>
       <c r="AK87" s="141">
         <f>FRE!$O$187-AK86</f>
@@ -19039,143 +19044,143 @@
       <c r="Q88" s="39"/>
       <c r="R88" s="40"/>
       <c r="S88" s="41"/>
-      <c r="T88" s="332" t="s">
+      <c r="T88" s="336" t="s">
         <v>197</v>
       </c>
-      <c r="U88" s="333"/>
+      <c r="U88" s="337"/>
       <c r="V88" s="32"/>
       <c r="W88" s="27"/>
-      <c r="X88" s="332" t="s">
+      <c r="X88" s="336" t="s">
         <v>197</v>
       </c>
-      <c r="Y88" s="333"/>
+      <c r="Y88" s="337"/>
       <c r="Z88" s="32"/>
       <c r="AA88" s="27"/>
-      <c r="AB88" s="332" t="s">
+      <c r="AB88" s="336" t="s">
         <v>197</v>
       </c>
-      <c r="AC88" s="333"/>
+      <c r="AC88" s="337"/>
       <c r="AD88" s="32"/>
       <c r="AE88" s="27"/>
-      <c r="AF88" s="332" t="s">
+      <c r="AF88" s="336" t="s">
         <v>197</v>
       </c>
-      <c r="AG88" s="333"/>
+      <c r="AG88" s="337"/>
       <c r="AH88" s="30"/>
     </row>
     <row r="89" spans="2:37" x14ac:dyDescent="0.3">
       <c r="I89" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="J89" s="246" t="str">
+      <c r="J89" s="260" t="str">
         <f>IF(FRE!$B$22="","",FRE!$B$22)</f>
         <v>{RESPONSÁVEL TÉCNICO}</v>
       </c>
-      <c r="K89" s="246"/>
-      <c r="L89" s="246"/>
+      <c r="K89" s="260"/>
+      <c r="L89" s="260"/>
       <c r="Q89" s="39"/>
       <c r="R89" s="40"/>
       <c r="S89" s="41"/>
-      <c r="T89" s="332" t="s">
+      <c r="T89" s="336" t="s">
         <v>198</v>
       </c>
-      <c r="U89" s="333"/>
+      <c r="U89" s="337"/>
       <c r="V89" s="32"/>
       <c r="W89" s="27"/>
-      <c r="X89" s="332" t="s">
+      <c r="X89" s="336" t="s">
         <v>198</v>
       </c>
-      <c r="Y89" s="333"/>
+      <c r="Y89" s="337"/>
       <c r="Z89" s="32"/>
       <c r="AA89" s="27"/>
-      <c r="AB89" s="332" t="s">
+      <c r="AB89" s="336" t="s">
         <v>198</v>
       </c>
-      <c r="AC89" s="333"/>
+      <c r="AC89" s="337"/>
       <c r="AD89" s="32"/>
       <c r="AE89" s="27"/>
-      <c r="AF89" s="332" t="s">
+      <c r="AF89" s="336" t="s">
         <v>198</v>
       </c>
-      <c r="AG89" s="333"/>
+      <c r="AG89" s="337"/>
       <c r="AH89" s="30"/>
     </row>
     <row r="90" spans="2:37" x14ac:dyDescent="0.3">
       <c r="I90" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="J90" s="338" t="str">
+      <c r="J90" s="332" t="str">
         <f>IF(FRE!$M$22="","",FRE!$M$22)</f>
         <v>{DOC. RESPONSÁVEL}</v>
       </c>
-      <c r="K90" s="338"/>
-      <c r="L90" s="338"/>
+      <c r="K90" s="332"/>
+      <c r="L90" s="332"/>
       <c r="Q90" s="39"/>
       <c r="R90" s="40"/>
       <c r="S90" s="134"/>
-      <c r="T90" s="332" t="s">
+      <c r="T90" s="336" t="s">
         <v>199</v>
       </c>
-      <c r="U90" s="333"/>
+      <c r="U90" s="337"/>
       <c r="V90" s="32"/>
       <c r="W90" s="27"/>
-      <c r="X90" s="332" t="s">
+      <c r="X90" s="336" t="s">
         <v>199</v>
       </c>
-      <c r="Y90" s="333"/>
+      <c r="Y90" s="337"/>
       <c r="Z90" s="32"/>
       <c r="AA90" s="27"/>
-      <c r="AB90" s="332" t="s">
+      <c r="AB90" s="336" t="s">
         <v>199</v>
       </c>
-      <c r="AC90" s="333"/>
+      <c r="AC90" s="337"/>
       <c r="AD90" s="32"/>
       <c r="AE90" s="27"/>
-      <c r="AF90" s="332" t="s">
+      <c r="AF90" s="336" t="s">
         <v>199</v>
       </c>
-      <c r="AG90" s="333"/>
+      <c r="AG90" s="337"/>
       <c r="AH90" s="27"/>
     </row>
     <row r="91" spans="2:37" x14ac:dyDescent="0.3">
       <c r="I91" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="J91" s="338" t="str">
+      <c r="J91" s="332" t="str">
         <f>IF(FRE!$J$22="","",FRE!$J$22)</f>
         <v>{CREA}</v>
       </c>
-      <c r="K91" s="338"/>
-      <c r="L91" s="338"/>
+      <c r="K91" s="332"/>
+      <c r="L91" s="332"/>
       <c r="Q91" s="39"/>
       <c r="R91" s="40"/>
       <c r="S91" s="134"/>
-      <c r="T91" s="334">
+      <c r="T91" s="338">
         <f>SUM(T42:T61,T66:T85)+70%*SUM(T63:T65)+50%*SUM(U29:U35)</f>
         <v>0.42949999999999999</v>
       </c>
-      <c r="U91" s="335"/>
+      <c r="U91" s="339"/>
       <c r="V91" s="46"/>
       <c r="W91" s="27"/>
-      <c r="X91" s="334">
+      <c r="X91" s="338">
         <f>SUM(X42:X61,X66:X85)+70%*SUM(X63:X65)+50%*SUM(Y29:Y35)</f>
         <v>0.43650000000000011</v>
       </c>
-      <c r="Y91" s="335"/>
+      <c r="Y91" s="339"/>
       <c r="Z91" s="46"/>
       <c r="AA91" s="27"/>
-      <c r="AB91" s="334">
+      <c r="AB91" s="338">
         <f>SUM(AB42:AB61,AB66:AB85)+70%*SUM(AB63:AB65)+50%*SUM(AC29:AC35)</f>
         <v>0.41550000000000004</v>
       </c>
-      <c r="AC91" s="335"/>
+      <c r="AC91" s="339"/>
       <c r="AD91" s="46"/>
       <c r="AE91" s="27"/>
-      <c r="AF91" s="334">
+      <c r="AF91" s="338">
         <f>SUM(AF42:AF61,AF66:AF85)+70%*SUM(AF63:AF65)+50%*SUM(AG29:AG35)</f>
         <v>0.41849999999999998</v>
       </c>
-      <c r="AG91" s="335"/>
+      <c r="AG91" s="339"/>
       <c r="AH91" s="27"/>
     </row>
     <row r="92" spans="2:37" x14ac:dyDescent="0.3">
@@ -19220,11 +19225,24 @@
     </row>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="J89:L89"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="AH21:AH24"/>
+    <mergeCell ref="V21:V24"/>
+    <mergeCell ref="X21:X24"/>
+    <mergeCell ref="Y21:Y24"/>
+    <mergeCell ref="Z21:Z24"/>
+    <mergeCell ref="AB21:AB24"/>
+    <mergeCell ref="AC21:AC24"/>
+    <mergeCell ref="T91:U91"/>
+    <mergeCell ref="X91:Y91"/>
+    <mergeCell ref="AB91:AC91"/>
+    <mergeCell ref="AF91:AG91"/>
+    <mergeCell ref="T90:U90"/>
+    <mergeCell ref="X90:Y90"/>
+    <mergeCell ref="AF89:AG89"/>
+    <mergeCell ref="T88:U88"/>
+    <mergeCell ref="X88:Y88"/>
+    <mergeCell ref="AB90:AC90"/>
+    <mergeCell ref="AF90:AG90"/>
     <mergeCell ref="J90:L90"/>
     <mergeCell ref="J91:L91"/>
     <mergeCell ref="AB87:AC87"/>
@@ -19241,24 +19259,11 @@
     <mergeCell ref="T89:U89"/>
     <mergeCell ref="X89:Y89"/>
     <mergeCell ref="AB89:AC89"/>
-    <mergeCell ref="AF89:AG89"/>
-    <mergeCell ref="T88:U88"/>
-    <mergeCell ref="X88:Y88"/>
-    <mergeCell ref="AB90:AC90"/>
-    <mergeCell ref="AF90:AG90"/>
-    <mergeCell ref="T91:U91"/>
-    <mergeCell ref="X91:Y91"/>
-    <mergeCell ref="AB91:AC91"/>
-    <mergeCell ref="AF91:AG91"/>
-    <mergeCell ref="T90:U90"/>
-    <mergeCell ref="X90:Y90"/>
-    <mergeCell ref="AH21:AH24"/>
-    <mergeCell ref="V21:V24"/>
-    <mergeCell ref="X21:X24"/>
-    <mergeCell ref="Y21:Y24"/>
-    <mergeCell ref="Z21:Z24"/>
-    <mergeCell ref="AB21:AB24"/>
-    <mergeCell ref="AC21:AC24"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="J89:L89"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="C22:E22"/>
   </mergeCells>
   <phoneticPr fontId="25" type="noConversion"/>
   <conditionalFormatting sqref="C22">
@@ -19340,10 +19345,10 @@
       <c r="A1" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="L1" s="321" t="s">
+      <c r="L1" s="242" t="s">
         <v>857</v>
       </c>
-      <c r="M1" s="322"/>
+      <c r="M1" s="243"/>
     </row>
     <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="54" t="s">
@@ -19352,10 +19357,10 @@
       <c r="E2" s="186" t="s">
         <v>524</v>
       </c>
-      <c r="L2" s="323" t="s">
+      <c r="L2" s="244" t="s">
         <v>858</v>
       </c>
-      <c r="M2" s="324"/>
+      <c r="M2" s="245"/>
     </row>
     <row r="3" spans="1:13" ht="8.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="54" t="s">
@@ -25771,36 +25776,36 @@
       <c r="J436" s="60" t="s">
         <v>57</v>
       </c>
-      <c r="K436" s="246" t="str">
+      <c r="K436" s="260" t="str">
         <f>IF(FRE!$B$22="","",FRE!$B$22)</f>
         <v>{RESPONSÁVEL TÉCNICO}</v>
       </c>
-      <c r="L436" s="246"/>
-      <c r="M436" s="246"/>
+      <c r="L436" s="260"/>
+      <c r="M436" s="260"/>
       <c r="N436" s="15"/>
     </row>
     <row r="437" spans="2:14" s="14" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="J437" s="60" t="s">
         <v>58</v>
       </c>
-      <c r="K437" s="338" t="str">
+      <c r="K437" s="332" t="str">
         <f>IF(FRE!$M$22="","",FRE!$M$22)</f>
         <v>{DOC. RESPONSÁVEL}</v>
       </c>
-      <c r="L437" s="338"/>
-      <c r="M437" s="338"/>
+      <c r="L437" s="332"/>
+      <c r="M437" s="332"/>
       <c r="N437" s="15"/>
     </row>
     <row r="438" spans="2:14" s="14" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="J438" s="60" t="s">
         <v>59</v>
       </c>
-      <c r="K438" s="338" t="str">
+      <c r="K438" s="332" t="str">
         <f>IF(FRE!$J$22="","",FRE!$J$22)</f>
         <v>{CREA}</v>
       </c>
-      <c r="L438" s="338"/>
-      <c r="M438" s="338"/>
+      <c r="L438" s="332"/>
+      <c r="M438" s="332"/>
       <c r="N438" s="15"/>
     </row>
     <row r="439" spans="2:14" s="14" customFormat="1" x14ac:dyDescent="0.2">
@@ -25820,57 +25825,32 @@
   </sheetData>
   <sheetProtection insertRows="0"/>
   <mergeCells count="95">
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="C217:H217"/>
-    <mergeCell ref="C216:H216"/>
-    <mergeCell ref="C40:H40"/>
-    <mergeCell ref="C42:H42"/>
-    <mergeCell ref="C52:H52"/>
-    <mergeCell ref="C90:H90"/>
-    <mergeCell ref="C102:H102"/>
-    <mergeCell ref="C113:H113"/>
-    <mergeCell ref="C199:H199"/>
-    <mergeCell ref="C246:H246"/>
-    <mergeCell ref="C253:H253"/>
-    <mergeCell ref="C227:H227"/>
-    <mergeCell ref="C238:H238"/>
-    <mergeCell ref="C159:H159"/>
-    <mergeCell ref="C171:H171"/>
-    <mergeCell ref="C182:H182"/>
-    <mergeCell ref="C191:H191"/>
-    <mergeCell ref="C61:H61"/>
-    <mergeCell ref="C123:H123"/>
-    <mergeCell ref="C132:H132"/>
-    <mergeCell ref="K436:M436"/>
-    <mergeCell ref="K437:M437"/>
-    <mergeCell ref="K438:M438"/>
-    <mergeCell ref="C414:H414"/>
-    <mergeCell ref="C260:H260"/>
-    <mergeCell ref="C385:H385"/>
-    <mergeCell ref="C386:H386"/>
-    <mergeCell ref="C112:H112"/>
-    <mergeCell ref="C412:H412"/>
-    <mergeCell ref="C361:H361"/>
-    <mergeCell ref="C362:H362"/>
-    <mergeCell ref="C375:H375"/>
-    <mergeCell ref="C376:H376"/>
-    <mergeCell ref="C395:H395"/>
-    <mergeCell ref="C405:H405"/>
-    <mergeCell ref="C406:H406"/>
-    <mergeCell ref="C403:H403"/>
-    <mergeCell ref="C319:H319"/>
-    <mergeCell ref="C326:H326"/>
-    <mergeCell ref="C355:H355"/>
-    <mergeCell ref="C288:H288"/>
-    <mergeCell ref="C289:H289"/>
-    <mergeCell ref="C309:H309"/>
-    <mergeCell ref="C402:H402"/>
-    <mergeCell ref="C384:H384"/>
-    <mergeCell ref="C394:H394"/>
-    <mergeCell ref="C399:H399"/>
-    <mergeCell ref="C396:H396"/>
-    <mergeCell ref="C153:H153"/>
+    <mergeCell ref="C122:H122"/>
+    <mergeCell ref="C131:H131"/>
+    <mergeCell ref="C140:H140"/>
+    <mergeCell ref="C141:H141"/>
+    <mergeCell ref="C383:H383"/>
+    <mergeCell ref="C413:H413"/>
+    <mergeCell ref="C245:H245"/>
+    <mergeCell ref="C252:H252"/>
+    <mergeCell ref="C259:H259"/>
+    <mergeCell ref="C334:H334"/>
+    <mergeCell ref="C404:H404"/>
+    <mergeCell ref="C41:H41"/>
+    <mergeCell ref="C80:H80"/>
+    <mergeCell ref="C89:H89"/>
+    <mergeCell ref="C101:H101"/>
+    <mergeCell ref="C59:H59"/>
+    <mergeCell ref="C50:H50"/>
+    <mergeCell ref="C67:H67"/>
+    <mergeCell ref="C68:H68"/>
+    <mergeCell ref="C55:H55"/>
+    <mergeCell ref="C56:H56"/>
+    <mergeCell ref="C57:H57"/>
+    <mergeCell ref="C58:H58"/>
+    <mergeCell ref="C69:H69"/>
+    <mergeCell ref="C81:H81"/>
+    <mergeCell ref="C60:H60"/>
     <mergeCell ref="C152:H152"/>
     <mergeCell ref="C327:H327"/>
     <mergeCell ref="C400:H400"/>
@@ -25886,35 +25866,60 @@
     <mergeCell ref="C335:H335"/>
     <mergeCell ref="C354:H354"/>
     <mergeCell ref="C158:H158"/>
-    <mergeCell ref="C41:H41"/>
-    <mergeCell ref="C80:H80"/>
-    <mergeCell ref="C89:H89"/>
-    <mergeCell ref="C101:H101"/>
-    <mergeCell ref="C59:H59"/>
-    <mergeCell ref="C50:H50"/>
-    <mergeCell ref="C67:H67"/>
-    <mergeCell ref="C68:H68"/>
-    <mergeCell ref="C55:H55"/>
-    <mergeCell ref="C56:H56"/>
-    <mergeCell ref="C57:H57"/>
-    <mergeCell ref="C58:H58"/>
-    <mergeCell ref="C69:H69"/>
-    <mergeCell ref="C81:H81"/>
-    <mergeCell ref="C60:H60"/>
     <mergeCell ref="C344:H344"/>
-    <mergeCell ref="C383:H383"/>
-    <mergeCell ref="C413:H413"/>
-    <mergeCell ref="C245:H245"/>
-    <mergeCell ref="C252:H252"/>
-    <mergeCell ref="C259:H259"/>
-    <mergeCell ref="C334:H334"/>
-    <mergeCell ref="C404:H404"/>
+    <mergeCell ref="C402:H402"/>
+    <mergeCell ref="C384:H384"/>
+    <mergeCell ref="C394:H394"/>
+    <mergeCell ref="C399:H399"/>
+    <mergeCell ref="C396:H396"/>
+    <mergeCell ref="C319:H319"/>
+    <mergeCell ref="C326:H326"/>
+    <mergeCell ref="C355:H355"/>
+    <mergeCell ref="C288:H288"/>
+    <mergeCell ref="C289:H289"/>
+    <mergeCell ref="C309:H309"/>
+    <mergeCell ref="K436:M436"/>
+    <mergeCell ref="K437:M437"/>
+    <mergeCell ref="K438:M438"/>
+    <mergeCell ref="C414:H414"/>
+    <mergeCell ref="C260:H260"/>
+    <mergeCell ref="C385:H385"/>
+    <mergeCell ref="C386:H386"/>
+    <mergeCell ref="C412:H412"/>
+    <mergeCell ref="C361:H361"/>
+    <mergeCell ref="C362:H362"/>
+    <mergeCell ref="C375:H375"/>
+    <mergeCell ref="C376:H376"/>
+    <mergeCell ref="C395:H395"/>
+    <mergeCell ref="C405:H405"/>
+    <mergeCell ref="C406:H406"/>
+    <mergeCell ref="C403:H403"/>
+    <mergeCell ref="C246:H246"/>
+    <mergeCell ref="C253:H253"/>
+    <mergeCell ref="C227:H227"/>
+    <mergeCell ref="C238:H238"/>
+    <mergeCell ref="C159:H159"/>
+    <mergeCell ref="C171:H171"/>
+    <mergeCell ref="C182:H182"/>
+    <mergeCell ref="C191:H191"/>
     <mergeCell ref="C170:H170"/>
     <mergeCell ref="C181:H181"/>
-    <mergeCell ref="C122:H122"/>
-    <mergeCell ref="C131:H131"/>
-    <mergeCell ref="C140:H140"/>
-    <mergeCell ref="C141:H141"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="C217:H217"/>
+    <mergeCell ref="C216:H216"/>
+    <mergeCell ref="C40:H40"/>
+    <mergeCell ref="C42:H42"/>
+    <mergeCell ref="C52:H52"/>
+    <mergeCell ref="C90:H90"/>
+    <mergeCell ref="C102:H102"/>
+    <mergeCell ref="C113:H113"/>
+    <mergeCell ref="C199:H199"/>
+    <mergeCell ref="C61:H61"/>
+    <mergeCell ref="C123:H123"/>
+    <mergeCell ref="C132:H132"/>
+    <mergeCell ref="C112:H112"/>
+    <mergeCell ref="C153:H153"/>
   </mergeCells>
   <phoneticPr fontId="25" type="noConversion"/>
   <conditionalFormatting sqref="B417:N428">
@@ -25955,10 +25960,10 @@
       <c r="A1" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="L1" s="321" t="s">
+      <c r="L1" s="242" t="s">
         <v>857</v>
       </c>
-      <c r="M1" s="322"/>
+      <c r="M1" s="243"/>
     </row>
     <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="54" t="s">
@@ -25967,10 +25972,10 @@
       <c r="E2" s="186" t="s">
         <v>733</v>
       </c>
-      <c r="L2" s="323" t="s">
+      <c r="L2" s="244" t="s">
         <v>858</v>
       </c>
-      <c r="M2" s="324"/>
+      <c r="M2" s="245"/>
     </row>
     <row r="3" spans="1:13" ht="8.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="54" t="s">
@@ -27324,36 +27329,36 @@
       <c r="J97" s="60" t="s">
         <v>57</v>
       </c>
-      <c r="K97" s="246" t="str">
+      <c r="K97" s="260" t="str">
         <f>IF(FRE!$B$22="","",FRE!$B$22)</f>
         <v>{RESPONSÁVEL TÉCNICO}</v>
       </c>
-      <c r="L97" s="246"/>
-      <c r="M97" s="246"/>
+      <c r="L97" s="260"/>
+      <c r="M97" s="260"/>
       <c r="N97" s="15"/>
     </row>
     <row r="98" spans="10:14" s="14" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="J98" s="60" t="s">
         <v>58</v>
       </c>
-      <c r="K98" s="338" t="str">
+      <c r="K98" s="332" t="str">
         <f>IF(FRE!$M$22="","",FRE!$M$22)</f>
         <v>{DOC. RESPONSÁVEL}</v>
       </c>
-      <c r="L98" s="338"/>
-      <c r="M98" s="338"/>
+      <c r="L98" s="332"/>
+      <c r="M98" s="332"/>
       <c r="N98" s="15"/>
     </row>
     <row r="99" spans="10:14" s="14" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="J99" s="60" t="s">
         <v>59</v>
       </c>
-      <c r="K99" s="338" t="str">
+      <c r="K99" s="332" t="str">
         <f>IF(FRE!$J$22="","",FRE!$J$22)</f>
         <v>{CREA}</v>
       </c>
-      <c r="L99" s="338"/>
-      <c r="M99" s="338"/>
+      <c r="L99" s="332"/>
+      <c r="M99" s="332"/>
       <c r="N99" s="15"/>
     </row>
     <row r="100" spans="10:14" s="14" customFormat="1" x14ac:dyDescent="0.2">
@@ -27373,6 +27378,17 @@
   </sheetData>
   <sheetProtection insertRows="0"/>
   <mergeCells count="27">
+    <mergeCell ref="E51:H51"/>
+    <mergeCell ref="C61:H61"/>
+    <mergeCell ref="C55:H55"/>
+    <mergeCell ref="K97:M97"/>
+    <mergeCell ref="E80:H80"/>
+    <mergeCell ref="C75:H75"/>
+    <mergeCell ref="C81:H81"/>
+    <mergeCell ref="K99:M99"/>
+    <mergeCell ref="K98:M98"/>
+    <mergeCell ref="C88:H88"/>
+    <mergeCell ref="C82:H82"/>
     <mergeCell ref="L1:M1"/>
     <mergeCell ref="L2:M2"/>
     <mergeCell ref="C32:H32"/>
@@ -27382,24 +27398,13 @@
     <mergeCell ref="C68:H68"/>
     <mergeCell ref="C46:H46"/>
     <mergeCell ref="C40:H40"/>
-    <mergeCell ref="K97:M97"/>
-    <mergeCell ref="E80:H80"/>
-    <mergeCell ref="C75:H75"/>
-    <mergeCell ref="C81:H81"/>
-    <mergeCell ref="K99:M99"/>
-    <mergeCell ref="K98:M98"/>
-    <mergeCell ref="C88:H88"/>
     <mergeCell ref="C23:H23"/>
     <mergeCell ref="C69:H69"/>
-    <mergeCell ref="C82:H82"/>
     <mergeCell ref="C22:H22"/>
     <mergeCell ref="C31:H31"/>
     <mergeCell ref="C39:H39"/>
     <mergeCell ref="C62:H62"/>
     <mergeCell ref="C47:H47"/>
-    <mergeCell ref="E51:H51"/>
-    <mergeCell ref="C61:H61"/>
-    <mergeCell ref="C55:H55"/>
   </mergeCells>
   <phoneticPr fontId="25" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -27436,10 +27441,10 @@
       <c r="A1" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="M1" s="321" t="s">
+      <c r="M1" s="242" t="s">
         <v>857</v>
       </c>
-      <c r="N1" s="322"/>
+      <c r="N1" s="243"/>
     </row>
     <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="54" t="s">
@@ -27448,10 +27453,10 @@
       <c r="E2" s="186" t="s">
         <v>654</v>
       </c>
-      <c r="M2" s="323" t="s">
+      <c r="M2" s="244" t="s">
         <v>858</v>
       </c>
-      <c r="N2" s="324"/>
+      <c r="N2" s="245"/>
     </row>
     <row r="3" spans="1:14" ht="8.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="54" t="s">
@@ -32575,36 +32580,36 @@
       <c r="J362" s="60" t="s">
         <v>57</v>
       </c>
-      <c r="K362" s="246" t="str">
+      <c r="K362" s="260" t="str">
         <f>IF(FRE!$B$22="","",FRE!$B$22)</f>
         <v>{RESPONSÁVEL TÉCNICO}</v>
       </c>
-      <c r="L362" s="246"/>
-      <c r="M362" s="246"/>
+      <c r="L362" s="260"/>
+      <c r="M362" s="260"/>
       <c r="N362" s="15"/>
     </row>
     <row r="363" spans="2:14" s="14" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="J363" s="60" t="s">
         <v>58</v>
       </c>
-      <c r="K363" s="338" t="str">
+      <c r="K363" s="332" t="str">
         <f>IF(FRE!$M$22="","",FRE!$M$22)</f>
         <v>{DOC. RESPONSÁVEL}</v>
       </c>
-      <c r="L363" s="338"/>
-      <c r="M363" s="338"/>
+      <c r="L363" s="332"/>
+      <c r="M363" s="332"/>
       <c r="N363" s="15"/>
     </row>
     <row r="364" spans="2:14" s="14" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="J364" s="60" t="s">
         <v>59</v>
       </c>
-      <c r="K364" s="338" t="str">
+      <c r="K364" s="332" t="str">
         <f>IF(FRE!$J$22="","",FRE!$J$22)</f>
         <v>{CREA}</v>
       </c>
-      <c r="L364" s="338"/>
-      <c r="M364" s="338"/>
+      <c r="L364" s="332"/>
+      <c r="M364" s="332"/>
       <c r="N364" s="15"/>
     </row>
     <row r="365" spans="2:14" s="14" customFormat="1" x14ac:dyDescent="0.2">
@@ -32623,30 +32628,20 @@
     </row>
   </sheetData>
   <mergeCells count="54">
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="C50:H50"/>
-    <mergeCell ref="C56:H56"/>
-    <mergeCell ref="C49:H49"/>
-    <mergeCell ref="C26:H26"/>
-    <mergeCell ref="C27:H27"/>
-    <mergeCell ref="C28:H28"/>
-    <mergeCell ref="C40:H40"/>
-    <mergeCell ref="C41:H41"/>
-    <mergeCell ref="C57:H57"/>
-    <mergeCell ref="C58:H58"/>
-    <mergeCell ref="C202:H202"/>
-    <mergeCell ref="C212:H212"/>
-    <mergeCell ref="C77:H77"/>
-    <mergeCell ref="C88:H88"/>
-    <mergeCell ref="C98:H98"/>
-    <mergeCell ref="C107:H107"/>
-    <mergeCell ref="C69:H69"/>
-    <mergeCell ref="C115:H115"/>
-    <mergeCell ref="C134:H134"/>
-    <mergeCell ref="C193:H193"/>
-    <mergeCell ref="C169:H169"/>
-    <mergeCell ref="C176:H176"/>
+    <mergeCell ref="C305:H305"/>
+    <mergeCell ref="C314:H314"/>
+    <mergeCell ref="C323:H323"/>
+    <mergeCell ref="C346:H346"/>
+    <mergeCell ref="C352:H352"/>
+    <mergeCell ref="C330:H330"/>
+    <mergeCell ref="C331:H331"/>
+    <mergeCell ref="C344:H344"/>
+    <mergeCell ref="C345:H345"/>
+    <mergeCell ref="C260:H260"/>
+    <mergeCell ref="C280:H280"/>
+    <mergeCell ref="C281:H281"/>
+    <mergeCell ref="C289:H289"/>
+    <mergeCell ref="C298:H298"/>
     <mergeCell ref="C353:H353"/>
     <mergeCell ref="K362:M362"/>
     <mergeCell ref="K363:M363"/>
@@ -32663,20 +32658,30 @@
     <mergeCell ref="C297:H297"/>
     <mergeCell ref="C324:H324"/>
     <mergeCell ref="C259:H259"/>
-    <mergeCell ref="C260:H260"/>
-    <mergeCell ref="C280:H280"/>
-    <mergeCell ref="C281:H281"/>
-    <mergeCell ref="C289:H289"/>
-    <mergeCell ref="C298:H298"/>
-    <mergeCell ref="C305:H305"/>
-    <mergeCell ref="C314:H314"/>
-    <mergeCell ref="C323:H323"/>
-    <mergeCell ref="C346:H346"/>
-    <mergeCell ref="C352:H352"/>
-    <mergeCell ref="C330:H330"/>
-    <mergeCell ref="C331:H331"/>
-    <mergeCell ref="C344:H344"/>
-    <mergeCell ref="C345:H345"/>
+    <mergeCell ref="C57:H57"/>
+    <mergeCell ref="C58:H58"/>
+    <mergeCell ref="C202:H202"/>
+    <mergeCell ref="C212:H212"/>
+    <mergeCell ref="C77:H77"/>
+    <mergeCell ref="C88:H88"/>
+    <mergeCell ref="C98:H98"/>
+    <mergeCell ref="C107:H107"/>
+    <mergeCell ref="C69:H69"/>
+    <mergeCell ref="C115:H115"/>
+    <mergeCell ref="C134:H134"/>
+    <mergeCell ref="C193:H193"/>
+    <mergeCell ref="C169:H169"/>
+    <mergeCell ref="C176:H176"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="C50:H50"/>
+    <mergeCell ref="C56:H56"/>
+    <mergeCell ref="C49:H49"/>
+    <mergeCell ref="C26:H26"/>
+    <mergeCell ref="C27:H27"/>
+    <mergeCell ref="C28:H28"/>
+    <mergeCell ref="C40:H40"/>
+    <mergeCell ref="C41:H41"/>
   </mergeCells>
   <phoneticPr fontId="25" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -32717,10 +32722,10 @@
       <c r="K1" s="20"/>
       <c r="L1" s="20"/>
       <c r="M1" s="20"/>
-      <c r="N1" s="321" t="s">
+      <c r="N1" s="242" t="s">
         <v>857</v>
       </c>
-      <c r="O1" s="322"/>
+      <c r="O1" s="243"/>
     </row>
     <row r="2" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="53" t="s">
@@ -32734,10 +32739,10 @@
       <c r="K2" s="20"/>
       <c r="L2" s="20"/>
       <c r="M2" s="20"/>
-      <c r="N2" s="323" t="s">
+      <c r="N2" s="244" t="s">
         <v>858</v>
       </c>
-      <c r="O2" s="324"/>
+      <c r="O2" s="245"/>
     </row>
     <row r="3" spans="1:15" ht="8.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="53" t="s">
@@ -32887,10 +32892,10 @@
       <c r="C17" s="104" t="s">
         <v>674</v>
       </c>
-      <c r="D17" s="256" t="s">
+      <c r="D17" s="315" t="s">
         <v>686</v>
       </c>
-      <c r="E17" s="256"/>
+      <c r="E17" s="315"/>
       <c r="F17" s="105"/>
       <c r="G17" s="105"/>
       <c r="H17" s="104" t="s">
@@ -32908,10 +32913,10 @@
       <c r="P17" s="107"/>
     </row>
     <row r="19" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="346" t="s">
+      <c r="B19" s="345" t="s">
         <v>685</v>
       </c>
-      <c r="C19" s="347"/>
+      <c r="C19" s="346"/>
       <c r="D19" s="108" t="str">
         <f>FRE!B186</f>
         <v>Edificações</v>
@@ -32921,11 +32926,11 @@
       <c r="G19" s="94"/>
       <c r="H19" s="94"/>
       <c r="I19" s="94"/>
-      <c r="J19" s="344">
+      <c r="J19" s="351">
         <f>FRE!M187</f>
         <v>0</v>
       </c>
-      <c r="K19" s="344"/>
+      <c r="K19" s="351"/>
       <c r="L19" s="200">
         <f>IF(SUM($J$19:$K$21)=0,0,J19/SUM($J$19:$K$21))</f>
         <v>0</v>
@@ -32936,8 +32941,8 @@
       <c r="P19" s="95"/>
     </row>
     <row r="20" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="348"/>
-      <c r="C20" s="349"/>
+      <c r="B20" s="347"/>
+      <c r="C20" s="348"/>
       <c r="D20" s="109" t="str">
         <f>FRE!B189</f>
         <v>Infraestrutura e urbanização</v>
@@ -32955,8 +32960,8 @@
       <c r="P20" s="97"/>
     </row>
     <row r="21" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="348"/>
-      <c r="C21" s="349"/>
+      <c r="B21" s="347"/>
+      <c r="C21" s="348"/>
       <c r="D21" s="109" t="str">
         <f>FRE!B192</f>
         <v>Equipamentos comunitários</v>
@@ -32974,8 +32979,8 @@
       <c r="P21" s="97"/>
     </row>
     <row r="22" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="348"/>
-      <c r="C22" s="349"/>
+      <c r="B22" s="347"/>
+      <c r="C22" s="348"/>
       <c r="D22" s="110"/>
       <c r="H22" s="98"/>
       <c r="I22" s="98"/>
@@ -32983,8 +32988,8 @@
       <c r="P22" s="97"/>
     </row>
     <row r="23" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="348"/>
-      <c r="C23" s="349"/>
+      <c r="B23" s="347"/>
+      <c r="C23" s="348"/>
       <c r="D23" s="111" t="s">
         <v>682</v>
       </c>
@@ -33001,8 +33006,8 @@
       <c r="P23" s="97"/>
     </row>
     <row r="24" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="348"/>
-      <c r="C24" s="349"/>
+      <c r="B24" s="347"/>
+      <c r="C24" s="348"/>
       <c r="D24" s="109" t="str">
         <f>IF(FRE!B209="","",FRE!B209)</f>
         <v/>
@@ -33020,8 +33025,8 @@
       <c r="P24" s="97"/>
     </row>
     <row r="25" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="348"/>
-      <c r="C25" s="349"/>
+      <c r="B25" s="347"/>
+      <c r="C25" s="348"/>
       <c r="D25" s="109" t="str">
         <f>IF(FRE!B210="","",FRE!B210)</f>
         <v/>
@@ -33039,8 +33044,8 @@
       <c r="P25" s="97"/>
     </row>
     <row r="26" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="350"/>
-      <c r="C26" s="351"/>
+      <c r="B26" s="349"/>
+      <c r="C26" s="350"/>
       <c r="D26" s="112" t="str">
         <f>IF(FRE!B211="","",FRE!B211)</f>
         <v/>
@@ -33050,11 +33055,11 @@
       <c r="G26" s="99"/>
       <c r="H26" s="99"/>
       <c r="I26" s="99"/>
-      <c r="J26" s="345">
+      <c r="J26" s="344">
         <f>FRE!G211</f>
         <v>0</v>
       </c>
-      <c r="K26" s="345"/>
+      <c r="K26" s="344"/>
       <c r="L26" s="201">
         <f>IF($J$23=0,0,J26/$J$23)</f>
         <v>0</v>
@@ -35513,6 +35518,9 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="K28:L28"/>
     <mergeCell ref="N1:O1"/>
     <mergeCell ref="N2:O2"/>
     <mergeCell ref="B28:B29"/>
@@ -35529,20 +35537,17 @@
     <mergeCell ref="J24:K24"/>
     <mergeCell ref="D17:E17"/>
     <mergeCell ref="J19:K19"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="K28:L28"/>
   </mergeCells>
   <phoneticPr fontId="25" type="noConversion"/>
   <conditionalFormatting sqref="B31:B78">
-    <cfRule type="expression" dxfId="31" priority="197" stopIfTrue="1">
-      <formula>AND(L31=100%,L30&lt;&gt;100%)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="30" priority="195" stopIfTrue="1">
+    <cfRule type="expression" dxfId="31" priority="195" stopIfTrue="1">
       <formula>AND(P31=100%,P30&lt;&gt;100%)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="29" priority="196" stopIfTrue="1">
+    <cfRule type="expression" dxfId="30" priority="196" stopIfTrue="1">
       <formula>AND(J31=100%,J30&lt;&gt;100%)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="29" priority="197" stopIfTrue="1">
+      <formula>AND(L31=100%,L30&lt;&gt;100%)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C30:C66">
@@ -35569,14 +35574,14 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E30:F78">
-    <cfRule type="expression" dxfId="23" priority="189" stopIfTrue="1">
-      <formula>$F30=100%</formula>
+    <cfRule type="expression" dxfId="23" priority="187" stopIfTrue="1">
+      <formula>OR(AND($B$27="não",$C$27&lt;&gt;$D$27,$C$27&lt;&gt;$E$27), $F29=100%)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="188" stopIfTrue="1">
       <formula>$F30&gt;100%</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="187" stopIfTrue="1">
-      <formula>OR(AND($B$27="não",$C$27&lt;&gt;$D$27,$C$27&lt;&gt;$E$27), $F29=100%)</formula>
+    <cfRule type="expression" dxfId="21" priority="189" stopIfTrue="1">
+      <formula>$F30=100%</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G28:H29">
@@ -35617,11 +35622,11 @@
     <cfRule type="expression" dxfId="12" priority="26" stopIfTrue="1">
       <formula>$L30&gt;100%</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="11" priority="28" stopIfTrue="1">
+    <cfRule type="expression" dxfId="11" priority="27" stopIfTrue="1">
+      <formula>$L29=100%</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="10" priority="28" stopIfTrue="1">
       <formula>$L30=100%</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="10" priority="27" stopIfTrue="1">
-      <formula>$L29=100%</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M55:M78">
@@ -35682,28 +35687,10 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="71ed10ea-0296-489a-81f6-10bdefde05fd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <TaxCatchAll xmlns="5586f595-ccd6-45ce-9490-0ddb8aaaf61c"/>
-  </documentManagement>
-</p:properties>
+<LongProperties xmlns="http://schemas.microsoft.com/office/2006/metadata/longProperties"/>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100E9844E6855F17549A33DFB208F4313F8" ma:contentTypeVersion="16" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="f08f11335cb0fb9e81096deba336cb0c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="71ed10ea-0296-489a-81f6-10bdefde05fd" xmlns:ns3="5586f595-ccd6-45ce-9490-0ddb8aaaf61c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2e453aa5d5d0958c5964eec1bbb582cc" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -35949,31 +35936,37 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<LongProperties xmlns="http://schemas.microsoft.com/office/2006/metadata/longProperties"/>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="71ed10ea-0296-489a-81f6-10bdefde05fd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <TaxCatchAll xmlns="5586f595-ccd6-45ce-9490-0ddb8aaaf61c"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E1C53012-60DF-4604-871C-6C2D9AA0C804}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32F68385-A023-4E12-B241-59312BEC7302}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="71ed10ea-0296-489a-81f6-10bdefde05fd"/>
-    <ds:schemaRef ds:uri="5586f595-ccd6-45ce-9490-0ddb8aaaf61c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/longProperties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24A1E1BA-2079-46D0-AABD-EA65D7930A83}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82291295-9DA5-47A7-BC3A-1915DD52A217}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -35993,10 +35986,22 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24A1E1BA-2079-46D0-AABD-EA65D7930A83}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32F68385-A023-4E12-B241-59312BEC7302}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E1C53012-60DF-4604-871C-6C2D9AA0C804}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/longProperties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="71ed10ea-0296-489a-81f6-10bdefde05fd"/>
+    <ds:schemaRef ds:uri="5586f595-ccd6-45ce-9490-0ddb8aaaf61c"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>